--- a/data/eps-estimates/DD_universe_EPS_estimates_20260917.xlsx
+++ b/data/eps-estimates/DD_universe_EPS_estimates_20260917.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB293"/>
+  <dimension ref="A1:BD293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,6 +688,16 @@
           <t>Last Price Local</t>
         </is>
       </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Short Interest % Float</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Insider Net Buy 3M</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -696,13 +706,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="C2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="D2" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="H2" t="n">
         <v>19.75</v>
@@ -777,10 +787,10 @@
         <v>145.82</v>
       </c>
       <c r="AG2" t="n">
-        <v>2600</v>
+        <v>2600000000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2610</v>
+        <v>2610000000</v>
       </c>
       <c r="AI2" t="n">
         <v>0.36</v>
@@ -798,7 +808,7 @@
         <v>93.95</v>
       </c>
       <c r="AN2" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="AO2" t="n">
         <v>25.4</v>
@@ -853,7 +863,7 @@
         <v>0.73</v>
       </c>
       <c r="D3" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="H3" t="n">
         <v>6.94</v>
@@ -928,10 +938,10 @@
         <v>32.74</v>
       </c>
       <c r="AG3" t="n">
-        <v>14130</v>
+        <v>14130000000</v>
       </c>
       <c r="AH3" t="n">
-        <v>14090</v>
+        <v>14090000000</v>
       </c>
       <c r="AI3" t="n">
         <v>83.77</v>
@@ -1082,10 +1092,10 @@
         <v>62.74</v>
       </c>
       <c r="AG4" t="n">
-        <v>2060</v>
+        <v>2060000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1990</v>
+        <v>1990000000</v>
       </c>
       <c r="AI4" t="n">
         <v>-1.44</v>
@@ -1103,7 +1113,7 @@
         <v>127.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AO4" t="n">
         <v>13.2</v>
@@ -1233,10 +1243,10 @@
         <v>32.49</v>
       </c>
       <c r="AG5" t="n">
-        <v>25930</v>
+        <v>25930000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>25930</v>
+        <v>25930000000</v>
       </c>
       <c r="AI5" t="n">
         <v>39.61</v>
@@ -1294,6 +1304,9 @@
       </c>
       <c r="BB5" t="n">
         <v>2380</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>15836</v>
       </c>
     </row>
     <row r="6">
@@ -1384,10 +1397,10 @@
         <v>76.29000000000001</v>
       </c>
       <c r="AG6" t="n">
-        <v>562.97</v>
+        <v>562970000</v>
       </c>
       <c r="AH6" t="n">
-        <v>565.16</v>
+        <v>565160000</v>
       </c>
       <c r="AJ6" t="n">
         <v>-219.46</v>
@@ -1532,10 +1545,10 @@
         <v>143.72</v>
       </c>
       <c r="AG7" t="n">
-        <v>508.22</v>
+        <v>508220000</v>
       </c>
       <c r="AH7" t="n">
-        <v>520.16</v>
+        <v>520160000</v>
       </c>
       <c r="AJ7" t="n">
         <v>-271.34</v>
@@ -1683,10 +1696,10 @@
         <v>39.99</v>
       </c>
       <c r="AG8" t="n">
-        <v>358.7</v>
+        <v>358700000</v>
       </c>
       <c r="AH8" t="n">
-        <v>343.39</v>
+        <v>343390000</v>
       </c>
       <c r="AJ8" t="n">
         <v>-476.8</v>
@@ -1750,13 +1763,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="C9" t="n">
-        <v>4.57</v>
+        <v>4.55</v>
       </c>
       <c r="D9" t="n">
-        <v>8.710000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="H9" t="n">
         <v>17.04</v>
@@ -1831,10 +1844,10 @@
         <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1600</v>
+        <v>1600000000</v>
       </c>
       <c r="AH9" t="n">
-        <v>1590</v>
+        <v>1590000000</v>
       </c>
       <c r="AI9" t="n">
         <v>80.38</v>
@@ -1852,7 +1865,7 @@
         <v>89.48</v>
       </c>
       <c r="AN9" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="AO9" t="n">
         <v>19.7</v>
@@ -1901,13 +1914,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="C10" t="n">
-        <v>4.93</v>
+        <v>4.91</v>
       </c>
       <c r="D10" t="n">
-        <v>6.19</v>
+        <v>6.17</v>
       </c>
       <c r="H10" t="n">
         <v>37.2</v>
@@ -1982,10 +1995,10 @@
         <v>198.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>397.75</v>
+        <v>397750000</v>
       </c>
       <c r="AH10" t="n">
-        <v>356.52</v>
+        <v>356520000</v>
       </c>
       <c r="AI10" t="n">
         <v>2.28</v>
@@ -2003,7 +2016,7 @@
         <v>51.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="AO10" t="n">
         <v>19</v>
@@ -2058,7 +2071,7 @@
         <v>1.18</v>
       </c>
       <c r="D11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H11" t="n">
         <v>5.35</v>
@@ -2133,10 +2146,10 @@
         <v>248.21</v>
       </c>
       <c r="AG11" t="n">
-        <v>1540</v>
+        <v>1540000000</v>
       </c>
       <c r="AH11" t="n">
-        <v>1540</v>
+        <v>1540000000</v>
       </c>
       <c r="AI11" t="n">
         <v>28.23</v>
@@ -2209,7 +2222,7 @@
         <v>0.54</v>
       </c>
       <c r="C12" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="D12" t="n">
         <v>0.98</v>
@@ -2290,10 +2303,10 @@
         <v>114.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>3280</v>
+        <v>3280000000</v>
       </c>
       <c r="AH12" t="n">
-        <v>2910</v>
+        <v>2910000000</v>
       </c>
       <c r="AI12" t="n">
         <v>57</v>
@@ -2444,10 +2457,10 @@
         <v>43.32</v>
       </c>
       <c r="AG13" t="n">
-        <v>134.59</v>
+        <v>134590000</v>
       </c>
       <c r="AH13" t="n">
-        <v>135.09</v>
+        <v>135090000</v>
       </c>
       <c r="AJ13" t="n">
         <v>-45.66</v>
@@ -2592,10 +2605,10 @@
         <v>35.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>145.41</v>
+        <v>145410000</v>
       </c>
       <c r="AH14" t="n">
-        <v>141.47</v>
+        <v>141470000</v>
       </c>
       <c r="AJ14" t="n">
         <v>-51.96</v>
@@ -2740,10 +2753,10 @@
         <v>-30.68</v>
       </c>
       <c r="AG15" t="n">
-        <v>82.92</v>
+        <v>82920000</v>
       </c>
       <c r="AH15" t="n">
-        <v>74.95</v>
+        <v>74950000</v>
       </c>
       <c r="AI15" t="n">
         <v>2.31</v>
@@ -2810,13 +2823,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6.22</v>
+        <v>6.2</v>
       </c>
       <c r="C16" t="n">
-        <v>10.8</v>
+        <v>10.76</v>
       </c>
       <c r="D16" t="n">
-        <v>14.93</v>
+        <v>14.87</v>
       </c>
       <c r="H16" t="n">
         <v>67.73999999999999</v>
@@ -2891,10 +2904,10 @@
         <v>21.73</v>
       </c>
       <c r="AG16" t="n">
-        <v>41.65</v>
+        <v>41650000</v>
       </c>
       <c r="AH16" t="n">
-        <v>41.84</v>
+        <v>41840000</v>
       </c>
       <c r="AI16" t="n">
         <v>-0.36</v>
@@ -2912,7 +2925,7 @@
         <v>47.66</v>
       </c>
       <c r="AN16" t="n">
-        <v>66.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="AO16" t="n">
         <v>56.4</v>
@@ -3030,10 +3043,10 @@
         <v>13.33</v>
       </c>
       <c r="AG17" t="n">
-        <v>108.77</v>
+        <v>108770000</v>
       </c>
       <c r="AH17" t="n">
-        <v>108.64</v>
+        <v>108640000</v>
       </c>
       <c r="AL17" t="n">
         <v>-1750</v>
@@ -3042,13 +3055,13 @@
         <v>398.76</v>
       </c>
       <c r="AN17" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="AO17" t="n">
         <v>30.3</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="AQ17" t="n">
         <v>8.800000000000001</v>
@@ -3160,10 +3173,10 @@
         <v>75.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>731.26</v>
+        <v>731260000</v>
       </c>
       <c r="AH18" t="n">
-        <v>750.83</v>
+        <v>750830000</v>
       </c>
       <c r="AI18" t="n">
         <v>29.14</v>
@@ -3184,7 +3197,7 @@
         <v>33.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AQ18" t="n">
         <v>12.1</v>
@@ -3305,10 +3318,10 @@
         <v>81.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>221.67</v>
+        <v>221670000</v>
       </c>
       <c r="AH19" t="n">
-        <v>208.01</v>
+        <v>208010000</v>
       </c>
       <c r="AI19" t="n">
         <v>12.29</v>
@@ -3456,10 +3469,10 @@
         <v>71.14</v>
       </c>
       <c r="AG20" t="n">
-        <v>8400</v>
+        <v>8400000000</v>
       </c>
       <c r="AH20" t="n">
-        <v>295.04</v>
+        <v>295040000</v>
       </c>
       <c r="AJ20" t="n">
         <v>-42.94</v>
@@ -3601,10 +3614,10 @@
         <v>48.31</v>
       </c>
       <c r="AG21" t="n">
-        <v>83.11</v>
+        <v>83110000</v>
       </c>
       <c r="AH21" t="n">
-        <v>81.15000000000001</v>
+        <v>81150000</v>
       </c>
       <c r="AI21" t="n">
         <v>19.9</v>
@@ -3622,13 +3635,13 @@
         <v>138.38</v>
       </c>
       <c r="AN21" t="n">
-        <v>27.1</v>
+        <v>27.8</v>
       </c>
       <c r="AO21" t="n">
         <v>38.6</v>
       </c>
       <c r="AP21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>8.6</v>
@@ -3656,6 +3669,9 @@
       </c>
       <c r="BB21" t="n">
         <v>64.18000000000001</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>-96975</v>
       </c>
     </row>
     <row r="22">
@@ -3746,10 +3762,10 @@
         <v>9.58</v>
       </c>
       <c r="AG22" t="n">
-        <v>15000</v>
+        <v>15000000000</v>
       </c>
       <c r="AH22" t="n">
-        <v>16330</v>
+        <v>16330000000</v>
       </c>
       <c r="AI22" t="n">
         <v>13710</v>
@@ -3810,6 +3826,12 @@
       </c>
       <c r="BB22" t="n">
         <v>332.41</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>-7194</v>
       </c>
     </row>
     <row r="23">
@@ -3891,10 +3913,10 @@
         <v>7.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>543.91</v>
+        <v>543910000</v>
       </c>
       <c r="AH23" t="n">
-        <v>104.93</v>
+        <v>104930000</v>
       </c>
       <c r="AI23" t="n">
         <v>1.49</v>
@@ -3912,7 +3934,7 @@
         <v>69.11</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AR23" t="n">
         <v>60.77</v>
@@ -3931,6 +3953,9 @@
       </c>
       <c r="BB23" t="n">
         <v>0.38</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4024,10 +4049,10 @@
         <v>15.48</v>
       </c>
       <c r="AG24" t="n">
-        <v>1770</v>
+        <v>1770000000</v>
       </c>
       <c r="AH24" t="n">
-        <v>1780</v>
+        <v>1780000000</v>
       </c>
       <c r="AI24" t="n">
         <v>1070</v>
@@ -4085,6 +4110,12 @@
       </c>
       <c r="BB24" t="n">
         <v>262.51</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>-32710</v>
       </c>
     </row>
     <row r="25">
@@ -4175,10 +4206,10 @@
         <v>-37.44</v>
       </c>
       <c r="AG25" t="n">
-        <v>623</v>
+        <v>623000000</v>
       </c>
       <c r="AH25" t="n">
-        <v>680</v>
+        <v>680000000</v>
       </c>
       <c r="AI25" t="n">
         <v>1710</v>
@@ -4233,6 +4264,12 @@
       </c>
       <c r="BB25" t="n">
         <v>167.51</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>-10249331</v>
       </c>
     </row>
     <row r="26">
@@ -4326,10 +4363,10 @@
         <v>11.11</v>
       </c>
       <c r="AG26" t="n">
-        <v>427</v>
+        <v>427000000</v>
       </c>
       <c r="AH26" t="n">
-        <v>470.9</v>
+        <v>470900000</v>
       </c>
       <c r="AI26" t="n">
         <v>1940</v>
@@ -4387,6 +4424,12 @@
       </c>
       <c r="BB26" t="n">
         <v>250.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>9933</v>
       </c>
     </row>
     <row r="27">
@@ -4480,10 +4523,10 @@
         <v>65.89</v>
       </c>
       <c r="AG27" t="n">
-        <v>496.71</v>
+        <v>496710000</v>
       </c>
       <c r="AH27" t="n">
-        <v>523.1799999999999</v>
+        <v>523180000</v>
       </c>
       <c r="AI27" t="n">
         <v>350.1</v>
@@ -4544,6 +4587,12 @@
       </c>
       <c r="BB27" t="n">
         <v>362.04</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>-50917</v>
       </c>
     </row>
     <row r="28">
@@ -4637,10 +4686,10 @@
         <v>5.71</v>
       </c>
       <c r="AG28" t="n">
-        <v>403.3</v>
+        <v>403300000</v>
       </c>
       <c r="AH28" t="n">
-        <v>415.7</v>
+        <v>415700000</v>
       </c>
       <c r="AI28" t="n">
         <v>242.6</v>
@@ -4698,6 +4747,12 @@
       </c>
       <c r="BB28" t="n">
         <v>273.19</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>68387</v>
       </c>
     </row>
     <row r="29">
@@ -4788,10 +4843,10 @@
         <v>36.86</v>
       </c>
       <c r="AG29" t="n">
-        <v>215</v>
+        <v>215000000</v>
       </c>
       <c r="AH29" t="n">
-        <v>218</v>
+        <v>218000000</v>
       </c>
       <c r="AI29" t="n">
         <v>706</v>
@@ -4849,6 +4904,12 @@
       </c>
       <c r="BB29" t="n">
         <v>220.31</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>22717</v>
       </c>
     </row>
     <row r="30">
@@ -4939,10 +5000,10 @@
         <v>83.43000000000001</v>
       </c>
       <c r="AG30" t="n">
-        <v>38.6</v>
+        <v>38600000</v>
       </c>
       <c r="AH30" t="n">
-        <v>37.72</v>
+        <v>37720000</v>
       </c>
       <c r="AI30" t="n">
         <v>68.59999999999999</v>
@@ -5003,6 +5064,12 @@
       </c>
       <c r="BB30" t="n">
         <v>252.22</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>-36753</v>
       </c>
     </row>
     <row r="31">
@@ -5096,10 +5163,10 @@
         <v>21.86</v>
       </c>
       <c r="AG31" t="n">
-        <v>1500</v>
+        <v>1500000000</v>
       </c>
       <c r="AH31" t="n">
-        <v>1500</v>
+        <v>1500000000</v>
       </c>
       <c r="AJ31" t="n">
         <v>-829.54</v>
@@ -5117,7 +5184,7 @@
         <v>15.8</v>
       </c>
       <c r="AO31" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AP31" t="n">
         <v>4.4</v>
@@ -5154,6 +5221,9 @@
       </c>
       <c r="BB31" t="n">
         <v>24.98</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -5235,10 +5305,10 @@
         <v>46398.61</v>
       </c>
       <c r="AG32" t="n">
-        <v>179.55</v>
+        <v>179550000</v>
       </c>
       <c r="AH32" t="n">
-        <v>34.17</v>
+        <v>34170000</v>
       </c>
       <c r="AI32" t="n">
         <v>195.02</v>
@@ -5262,7 +5332,7 @@
         <v>27.1</v>
       </c>
       <c r="AR32" t="n">
-        <v>43.78</v>
+        <v>43.77</v>
       </c>
       <c r="AS32" t="n">
         <v>111.15</v>
@@ -5290,6 +5360,12 @@
       </c>
       <c r="BB32" t="n">
         <v>269.18</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>-590793</v>
       </c>
     </row>
     <row r="33">
@@ -5377,10 +5453,10 @@
         <v>84.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>134.68</v>
+        <v>134680000</v>
       </c>
       <c r="AH33" t="n">
-        <v>121.69</v>
+        <v>121690000</v>
       </c>
       <c r="AI33" t="n">
         <v>336.62</v>
@@ -5407,7 +5483,7 @@
         <v>140.8</v>
       </c>
       <c r="AR33" t="n">
-        <v>44.77</v>
+        <v>44.75</v>
       </c>
       <c r="AS33" t="n">
         <v>-24.94</v>
@@ -5435,6 +5511,12 @@
       </c>
       <c r="BB33" t="n">
         <v>239.36</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -5528,10 +5610,10 @@
         <v>-4.17</v>
       </c>
       <c r="AG34" t="n">
-        <v>76.90000000000001</v>
+        <v>76900000</v>
       </c>
       <c r="AH34" t="n">
-        <v>87.2</v>
+        <v>87200000</v>
       </c>
       <c r="AI34" t="n">
         <v>20</v>
@@ -5592,6 +5674,12 @@
       </c>
       <c r="BB34" t="n">
         <v>115.87</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -5682,10 +5770,10 @@
         <v>-5.47</v>
       </c>
       <c r="AG35" t="n">
-        <v>808</v>
+        <v>808000000</v>
       </c>
       <c r="AH35" t="n">
-        <v>877</v>
+        <v>877000000</v>
       </c>
       <c r="AI35" t="n">
         <v>693</v>
@@ -5746,6 +5834,12 @@
       </c>
       <c r="BB35" t="n">
         <v>415.38</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>-96667</v>
       </c>
     </row>
     <row r="36">
@@ -5833,10 +5927,10 @@
         <v>65.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>1640</v>
+        <v>1640000000</v>
       </c>
       <c r="AH36" t="n">
-        <v>1570</v>
+        <v>1570000000</v>
       </c>
       <c r="AI36" t="n">
         <v>1900</v>
@@ -5897,6 +5991,12 @@
       </c>
       <c r="BB36" t="n">
         <v>512.5</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>-65136</v>
       </c>
     </row>
     <row r="37">
@@ -5990,10 +6090,10 @@
         <v>37.08</v>
       </c>
       <c r="AG37" t="n">
-        <v>248.45</v>
+        <v>248450000</v>
       </c>
       <c r="AH37" t="n">
-        <v>246.21</v>
+        <v>246210000</v>
       </c>
       <c r="AI37" t="n">
         <v>20.1</v>
@@ -6051,6 +6151,12 @@
       </c>
       <c r="BB37" t="n">
         <v>46.28</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>389855</v>
       </c>
     </row>
     <row r="38">
@@ -6141,10 +6247,10 @@
         <v>3.84</v>
       </c>
       <c r="AG38" t="n">
-        <v>98.2</v>
+        <v>98200000</v>
       </c>
       <c r="AH38" t="n">
-        <v>113.7</v>
+        <v>113700000</v>
       </c>
       <c r="AI38" t="n">
         <v>235</v>
@@ -6202,6 +6308,12 @@
       </c>
       <c r="BB38" t="n">
         <v>540.86</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>-117340</v>
       </c>
     </row>
     <row r="39">
@@ -6295,10 +6407,10 @@
         <v>6.01</v>
       </c>
       <c r="AG39" t="n">
-        <v>10830</v>
+        <v>10830000000</v>
       </c>
       <c r="AH39" t="n">
-        <v>10190</v>
+        <v>10190000000</v>
       </c>
       <c r="AI39" t="n">
         <v>19310</v>
@@ -6328,7 +6440,7 @@
         <v>8.4</v>
       </c>
       <c r="AR39" t="n">
-        <v>39.48</v>
+        <v>39.45</v>
       </c>
       <c r="AS39" t="n">
         <v>16.16</v>
@@ -6356,6 +6468,12 @@
       </c>
       <c r="BB39" t="n">
         <v>245.96</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>-1660771</v>
       </c>
     </row>
     <row r="40">
@@ -6446,10 +6564,10 @@
         <v>29.17</v>
       </c>
       <c r="AG40" t="n">
-        <v>1280</v>
+        <v>1280000000</v>
       </c>
       <c r="AH40" t="n">
-        <v>1270</v>
+        <v>1270000000</v>
       </c>
       <c r="AI40" t="n">
         <v>502.3</v>
@@ -6510,6 +6628,12 @@
       </c>
       <c r="BB40" t="n">
         <v>197.54</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>-4108714</v>
       </c>
     </row>
     <row r="41">
@@ -6603,10 +6727,10 @@
         <v>83.13</v>
       </c>
       <c r="AG41" t="n">
-        <v>2560</v>
+        <v>2560000000</v>
       </c>
       <c r="AH41" t="n">
-        <v>2480</v>
+        <v>2480000000</v>
       </c>
       <c r="AI41" t="n">
         <v>157.1</v>
@@ -6667,6 +6791,12 @@
       </c>
       <c r="BB41" t="n">
         <v>77.26000000000001</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>-2307702</v>
       </c>
     </row>
     <row r="42">
@@ -6760,10 +6890,10 @@
         <v>102.96</v>
       </c>
       <c r="AG42" t="n">
-        <v>341.97</v>
+        <v>341970000</v>
       </c>
       <c r="AH42" t="n">
-        <v>371.57</v>
+        <v>371570000</v>
       </c>
       <c r="AI42" t="n">
         <v>283.54</v>
@@ -6818,6 +6948,12 @@
       </c>
       <c r="BB42" t="n">
         <v>326.56</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>26316</v>
       </c>
     </row>
     <row r="43">
@@ -6905,10 +7041,10 @@
         <v>7.32</v>
       </c>
       <c r="AG43" t="n">
-        <v>1070</v>
+        <v>1070000000</v>
       </c>
       <c r="AH43" t="n">
-        <v>1030</v>
+        <v>1030000000</v>
       </c>
       <c r="AI43" t="n">
         <v>1150</v>
@@ -6960,6 +7096,9 @@
       </c>
       <c r="BB43" t="n">
         <v>243.98</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="44">
@@ -7053,10 +7192,10 @@
         <v>13.61</v>
       </c>
       <c r="AG44" t="n">
-        <v>52.26</v>
+        <v>52260000</v>
       </c>
       <c r="AH44" t="n">
-        <v>65.45</v>
+        <v>65450000</v>
       </c>
       <c r="AI44" t="n">
         <v>20.1</v>
@@ -7117,6 +7256,12 @@
       </c>
       <c r="BB44" t="n">
         <v>211.7</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>-5414</v>
       </c>
     </row>
     <row r="45">
@@ -7207,10 +7352,10 @@
         <v>2.25</v>
       </c>
       <c r="AG45" t="n">
-        <v>388.9</v>
+        <v>388900000</v>
       </c>
       <c r="AH45" t="n">
-        <v>398</v>
+        <v>398000000</v>
       </c>
       <c r="AI45" t="n">
         <v>231.07</v>
@@ -7259,6 +7404,9 @@
       </c>
       <c r="BB45" t="n">
         <v>1602.22</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>125</v>
       </c>
     </row>
     <row r="46">
@@ -7349,10 +7497,10 @@
         <v>16.08</v>
       </c>
       <c r="AG46" t="n">
-        <v>141.8</v>
+        <v>141800000</v>
       </c>
       <c r="AH46" t="n">
-        <v>151.2</v>
+        <v>151200000</v>
       </c>
       <c r="AI46" t="n">
         <v>28.5</v>
@@ -7413,6 +7561,12 @@
       </c>
       <c r="BB46" t="n">
         <v>189.65</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>-169443</v>
       </c>
     </row>
     <row r="47">
@@ -7503,10 +7657,10 @@
         <v>42.1</v>
       </c>
       <c r="AG47" t="n">
-        <v>4850</v>
+        <v>4850000000</v>
       </c>
       <c r="AH47" t="n">
-        <v>4230</v>
+        <v>4230000000</v>
       </c>
       <c r="AI47" t="n">
         <v>8480</v>
@@ -7567,6 +7721,12 @@
       </c>
       <c r="BB47" t="n">
         <v>339.51</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>-1074786</v>
       </c>
     </row>
     <row r="48">
@@ -7660,10 +7820,10 @@
         <v>120.26</v>
       </c>
       <c r="AG48" t="n">
-        <v>83.42</v>
+        <v>83420000</v>
       </c>
       <c r="AH48" t="n">
-        <v>93.37</v>
+        <v>93370000</v>
       </c>
       <c r="AI48" t="n">
         <v>48.69</v>
@@ -7724,6 +7884,12 @@
       </c>
       <c r="BB48" t="n">
         <v>92.73</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>187763</v>
       </c>
     </row>
     <row r="49">
@@ -7808,10 +7974,10 @@
         <v>-8.220000000000001</v>
       </c>
       <c r="AG49" t="n">
-        <v>43.93</v>
+        <v>43930000</v>
       </c>
       <c r="AH49" t="n">
-        <v>42.72</v>
+        <v>42720000</v>
       </c>
       <c r="AI49" t="n">
         <v>3.81</v>
@@ -7866,6 +8032,12 @@
       </c>
       <c r="BB49" t="n">
         <v>64.3</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>-6500</v>
       </c>
     </row>
     <row r="50">
@@ -7956,10 +8128,10 @@
         <v>-1.44</v>
       </c>
       <c r="AG50" t="n">
-        <v>240.4</v>
+        <v>240400000</v>
       </c>
       <c r="AH50" t="n">
-        <v>185.91</v>
+        <v>185910000</v>
       </c>
       <c r="AI50" t="n">
         <v>196.04</v>
@@ -8017,6 +8189,12 @@
       </c>
       <c r="BB50" t="n">
         <v>270.02</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>-353119</v>
       </c>
     </row>
     <row r="51">
@@ -8107,10 +8285,10 @@
         <v>11.14</v>
       </c>
       <c r="AG51" t="n">
-        <v>79.75</v>
+        <v>79750000</v>
       </c>
       <c r="AH51" t="n">
-        <v>85.53</v>
+        <v>85530000</v>
       </c>
       <c r="AI51" t="n">
         <v>20.24</v>
@@ -8171,6 +8349,9 @@
       </c>
       <c r="BB51" t="n">
         <v>178.85</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -8264,10 +8445,10 @@
         <v>29.36</v>
       </c>
       <c r="AG52" t="n">
-        <v>5090</v>
+        <v>5090000000</v>
       </c>
       <c r="AH52" t="n">
-        <v>5070</v>
+        <v>5070000000</v>
       </c>
       <c r="AI52" t="n">
         <v>123</v>
@@ -8285,13 +8466,13 @@
         <v>17.72</v>
       </c>
       <c r="AN52" t="n">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
       <c r="AO52" t="n">
         <v>11.3</v>
       </c>
       <c r="AP52" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ52" t="n">
         <v>3.3</v>
@@ -8316,6 +8497,9 @@
       </c>
       <c r="BB52" t="n">
         <v>84.14</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>22917</v>
       </c>
     </row>
     <row r="53">
@@ -8409,10 +8593,10 @@
         <v>16.85</v>
       </c>
       <c r="AG53" t="n">
-        <v>815.98</v>
+        <v>815980000</v>
       </c>
       <c r="AH53" t="n">
-        <v>1000</v>
+        <v>1000000000</v>
       </c>
       <c r="AI53" t="n">
         <v>601</v>
@@ -8467,6 +8651,12 @@
       </c>
       <c r="BB53" t="n">
         <v>171.4</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>-81550</v>
       </c>
     </row>
     <row r="54">
@@ -8560,10 +8750,10 @@
         <v>14.76</v>
       </c>
       <c r="AG54" t="n">
-        <v>160.87</v>
+        <v>160870000</v>
       </c>
       <c r="AH54" t="n">
-        <v>152.44</v>
+        <v>152440000</v>
       </c>
       <c r="AI54" t="n">
         <v>1460</v>
@@ -8621,6 +8811,12 @@
       </c>
       <c r="BB54" t="n">
         <v>1037.24</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>-27490</v>
       </c>
     </row>
     <row r="55">
@@ -8681,10 +8877,10 @@
         <v>15.5</v>
       </c>
       <c r="AG55" t="n">
-        <v>723.27</v>
+        <v>723270000</v>
       </c>
       <c r="AH55" t="n">
-        <v>665.71</v>
+        <v>665710000</v>
       </c>
       <c r="AI55" t="n">
         <v>1320</v>
@@ -8733,6 +8929,9 @@
       </c>
       <c r="BB55" t="n">
         <v>172.6</v>
+      </c>
+      <c r="BD55" t="n">
+        <v>-71434</v>
       </c>
     </row>
     <row r="56">
@@ -8826,10 +9025,10 @@
         <v>25.88</v>
       </c>
       <c r="AG56" t="n">
-        <v>2040</v>
+        <v>2040000000</v>
       </c>
       <c r="AH56" t="n">
-        <v>2150</v>
+        <v>2150000000</v>
       </c>
       <c r="AI56" t="n">
         <v>553</v>
@@ -8887,6 +9086,12 @@
       </c>
       <c r="BB56" t="n">
         <v>63.6</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD56" t="n">
+        <v>-7982</v>
       </c>
     </row>
     <row r="57">
@@ -8980,10 +9185,10 @@
         <v>31.77</v>
       </c>
       <c r="AG57" t="n">
-        <v>1490</v>
+        <v>1490000000</v>
       </c>
       <c r="AH57" t="n">
-        <v>1440</v>
+        <v>1440000000</v>
       </c>
       <c r="AI57" t="n">
         <v>320</v>
@@ -9044,6 +9249,12 @@
       </c>
       <c r="BB57" t="n">
         <v>43.91</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD57" t="n">
+        <v>295821</v>
       </c>
     </row>
     <row r="58">
@@ -9137,10 +9348,10 @@
         <v>17.89</v>
       </c>
       <c r="AG58" t="n">
-        <v>216.4</v>
+        <v>216400000</v>
       </c>
       <c r="AH58" t="n">
-        <v>236.8</v>
+        <v>236800000</v>
       </c>
       <c r="AI58" t="n">
         <v>59</v>
@@ -9201,6 +9412,12 @@
       </c>
       <c r="BB58" t="n">
         <v>62.27</v>
+      </c>
+      <c r="BC58" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>-144075</v>
       </c>
     </row>
     <row r="59">
@@ -9294,10 +9511,10 @@
         <v>11.97</v>
       </c>
       <c r="AG59" t="n">
-        <v>91.86</v>
+        <v>91860000</v>
       </c>
       <c r="AH59" t="n">
-        <v>91.7</v>
+        <v>91700000</v>
       </c>
       <c r="AI59" t="n">
         <v>32.78</v>
@@ -9358,6 +9575,12 @@
       </c>
       <c r="BB59" t="n">
         <v>145.66</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>-9558</v>
       </c>
     </row>
     <row r="60">
@@ -9430,10 +9653,10 @@
         <v>50.56</v>
       </c>
       <c r="AG60" t="n">
-        <v>780.22</v>
+        <v>780220000</v>
       </c>
       <c r="AH60" t="n">
-        <v>740.9400000000001</v>
+        <v>740940000</v>
       </c>
       <c r="AI60" t="n">
         <v>1580</v>
@@ -9491,6 +9714,12 @@
       </c>
       <c r="BB60" t="n">
         <v>123.45</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>-84045</v>
       </c>
     </row>
     <row r="61">
@@ -9584,10 +9813,10 @@
         <v>34.02</v>
       </c>
       <c r="AG61" t="n">
-        <v>237</v>
+        <v>237000000</v>
       </c>
       <c r="AH61" t="n">
-        <v>262</v>
+        <v>262000000</v>
       </c>
       <c r="AI61" t="n">
         <v>368</v>
@@ -9645,6 +9874,12 @@
       </c>
       <c r="BB61" t="n">
         <v>232.54</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD61" t="n">
+        <v>2085</v>
       </c>
     </row>
     <row r="62">
@@ -9732,10 +9967,10 @@
         <v>9.58</v>
       </c>
       <c r="AG62" t="n">
-        <v>49.97</v>
+        <v>49970000</v>
       </c>
       <c r="AH62" t="n">
-        <v>48.23</v>
+        <v>48230000</v>
       </c>
       <c r="AI62" t="n">
         <v>16.89</v>
@@ -9787,6 +10022,12 @@
       </c>
       <c r="BB62" t="n">
         <v>138.59</v>
+      </c>
+      <c r="BC62" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD62" t="n">
+        <v>-29174</v>
       </c>
     </row>
     <row r="63">
@@ -9880,10 +10121,10 @@
         <v>-75.27</v>
       </c>
       <c r="AG63" t="n">
-        <v>862.4</v>
+        <v>862400000</v>
       </c>
       <c r="AH63" t="n">
-        <v>861.2</v>
+        <v>861200000</v>
       </c>
       <c r="AI63" t="n">
         <v>64</v>
@@ -9944,6 +10185,12 @@
       </c>
       <c r="BB63" t="n">
         <v>54.26</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>2600</v>
       </c>
     </row>
     <row r="64">
@@ -10037,10 +10284,10 @@
         <v>-1.45</v>
       </c>
       <c r="AG64" t="n">
-        <v>472.3</v>
+        <v>472300000</v>
       </c>
       <c r="AH64" t="n">
-        <v>530.4</v>
+        <v>530400000</v>
       </c>
       <c r="AI64" t="n">
         <v>257</v>
@@ -10101,6 +10348,12 @@
       </c>
       <c r="BB64" t="n">
         <v>782.72</v>
+      </c>
+      <c r="BC64" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BD64" t="n">
+        <v>-44403</v>
       </c>
     </row>
     <row r="65">
@@ -10191,10 +10444,10 @@
         <v>44.93</v>
       </c>
       <c r="AG65" t="n">
-        <v>105.1</v>
+        <v>105100000</v>
       </c>
       <c r="AH65" t="n">
-        <v>106.7</v>
+        <v>106700000</v>
       </c>
       <c r="AI65" t="n">
         <v>53.2</v>
@@ -10221,7 +10474,7 @@
         <v>4.7</v>
       </c>
       <c r="AR65" t="n">
-        <v>36.05</v>
+        <v>35.79</v>
       </c>
       <c r="AS65" t="n">
         <v>-7.32</v>
@@ -10252,6 +10505,12 @@
       </c>
       <c r="BB65" t="n">
         <v>270.43</v>
+      </c>
+      <c r="BC65" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD65" t="n">
+        <v>-1274</v>
       </c>
     </row>
     <row r="66">
@@ -10345,10 +10604,10 @@
         <v>1.55</v>
       </c>
       <c r="AG66" t="n">
-        <v>273.31</v>
+        <v>273310000</v>
       </c>
       <c r="AH66" t="n">
-        <v>275.01</v>
+        <v>275010000</v>
       </c>
       <c r="AI66" t="n">
         <v>514.3099999999999</v>
@@ -10409,6 +10668,12 @@
       </c>
       <c r="BB66" t="n">
         <v>279.9</v>
+      </c>
+      <c r="BC66" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD66" t="n">
+        <v>-20632</v>
       </c>
     </row>
     <row r="67">
@@ -10499,10 +10764,10 @@
         <v>117.23</v>
       </c>
       <c r="AG67" t="n">
-        <v>254.91</v>
+        <v>254910000</v>
       </c>
       <c r="AH67" t="n">
-        <v>226.95</v>
+        <v>226950000</v>
       </c>
       <c r="AI67" t="n">
         <v>34.78</v>
@@ -10563,6 +10828,12 @@
       </c>
       <c r="BB67" t="n">
         <v>28.25</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>-2942188</v>
       </c>
     </row>
     <row r="68">
@@ -10656,10 +10927,10 @@
         <v>17</v>
       </c>
       <c r="AG68" t="n">
-        <v>46</v>
+        <v>46000000</v>
       </c>
       <c r="AH68" t="n">
-        <v>38.74</v>
+        <v>38740000</v>
       </c>
       <c r="AI68" t="n">
         <v>24.44</v>
@@ -10720,6 +10991,12 @@
       </c>
       <c r="BB68" t="n">
         <v>109.68</v>
+      </c>
+      <c r="BC68" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="BD68" t="n">
+        <v>-137752</v>
       </c>
     </row>
     <row r="69">
@@ -10810,10 +11087,10 @@
         <v>0.53</v>
       </c>
       <c r="AG69" t="n">
-        <v>425.8</v>
+        <v>425800000</v>
       </c>
       <c r="AH69" t="n">
-        <v>427.77</v>
+        <v>427770000</v>
       </c>
       <c r="AI69" t="n">
         <v>297.9</v>
@@ -10874,6 +11151,12 @@
       </c>
       <c r="BB69" t="n">
         <v>20.91</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>-46172</v>
       </c>
     </row>
     <row r="70">
@@ -10967,10 +11250,10 @@
         <v>91.68000000000001</v>
       </c>
       <c r="AG70" t="n">
-        <v>145.25</v>
+        <v>145250000</v>
       </c>
       <c r="AH70" t="n">
-        <v>152.19</v>
+        <v>152190000</v>
       </c>
       <c r="AI70" t="n">
         <v>212.21</v>
@@ -11031,6 +11314,12 @@
       </c>
       <c r="BB70" t="n">
         <v>340.5</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>-63741</v>
       </c>
     </row>
     <row r="71">
@@ -11124,10 +11413,10 @@
         <v>3</v>
       </c>
       <c r="AG71" t="n">
-        <v>811.1</v>
+        <v>811100000</v>
       </c>
       <c r="AH71" t="n">
-        <v>838.8</v>
+        <v>838800000</v>
       </c>
       <c r="AI71" t="n">
         <v>178</v>
@@ -11188,6 +11477,12 @@
       </c>
       <c r="BB71" t="n">
         <v>87.02</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>-359412</v>
       </c>
     </row>
     <row r="72">
@@ -11281,10 +11576,10 @@
         <v>50.76</v>
       </c>
       <c r="AG72" t="n">
-        <v>116.2</v>
+        <v>116200000</v>
       </c>
       <c r="AH72" t="n">
-        <v>123.6</v>
+        <v>123600000</v>
       </c>
       <c r="AI72" t="n">
         <v>80.90000000000001</v>
@@ -11336,6 +11631,9 @@
       </c>
       <c r="BB72" t="n">
         <v>323.83</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>-391440</v>
       </c>
     </row>
     <row r="73">
@@ -11429,10 +11727,10 @@
         <v>6</v>
       </c>
       <c r="AG73" t="n">
-        <v>1340</v>
+        <v>1340000000</v>
       </c>
       <c r="AH73" t="n">
-        <v>1400</v>
+        <v>1400000000</v>
       </c>
       <c r="AI73" t="n">
         <v>98.91</v>
@@ -11493,6 +11791,12 @@
       </c>
       <c r="BB73" t="n">
         <v>33.68</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>-34588</v>
       </c>
     </row>
     <row r="74">
@@ -11586,10 +11890,10 @@
         <v>-4.8</v>
       </c>
       <c r="AG74" t="n">
-        <v>138.7</v>
+        <v>138700000</v>
       </c>
       <c r="AH74" t="n">
-        <v>142.3</v>
+        <v>142300000</v>
       </c>
       <c r="AI74" t="n">
         <v>93</v>
@@ -11650,6 +11954,12 @@
       </c>
       <c r="BB74" t="n">
         <v>527.5</v>
+      </c>
+      <c r="BC74" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD74" t="n">
+        <v>-698</v>
       </c>
     </row>
     <row r="75">
@@ -11707,10 +12017,10 @@
         <v>51.58</v>
       </c>
       <c r="AG75" t="n">
-        <v>541.3</v>
+        <v>541300000</v>
       </c>
       <c r="AH75" t="n">
-        <v>393.2</v>
+        <v>393200000</v>
       </c>
       <c r="AI75" t="n">
         <v>773</v>
@@ -11768,6 +12078,12 @@
       </c>
       <c r="BB75" t="n">
         <v>203.19</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>-36161</v>
       </c>
     </row>
     <row r="76">
@@ -11861,10 +12177,10 @@
         <v>49.35</v>
       </c>
       <c r="AG76" t="n">
-        <v>195.39</v>
+        <v>195390000</v>
       </c>
       <c r="AH76" t="n">
-        <v>137.58</v>
+        <v>137580000</v>
       </c>
       <c r="AI76" t="n">
         <v>193.8</v>
@@ -11925,6 +12241,12 @@
       </c>
       <c r="BB76" t="n">
         <v>289.93</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>4840</v>
       </c>
     </row>
     <row r="77">
@@ -12015,10 +12337,10 @@
         <v>-79.86</v>
       </c>
       <c r="AG77" t="n">
-        <v>287.21</v>
+        <v>287210000</v>
       </c>
       <c r="AH77" t="n">
-        <v>222.34</v>
+        <v>222340000</v>
       </c>
       <c r="AI77" t="n">
         <v>938.95</v>
@@ -12073,6 +12395,12 @@
       </c>
       <c r="BB77" t="n">
         <v>164.51</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>-44355</v>
       </c>
     </row>
     <row r="78">
@@ -12166,10 +12494,10 @@
         <v>36.1</v>
       </c>
       <c r="AG78" t="n">
-        <v>195.21</v>
+        <v>195210000</v>
       </c>
       <c r="AH78" t="n">
-        <v>211.21</v>
+        <v>211210000</v>
       </c>
       <c r="AI78" t="n">
         <v>148.73</v>
@@ -12230,6 +12558,12 @@
       </c>
       <c r="BB78" t="n">
         <v>318.5</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>-7321</v>
       </c>
     </row>
     <row r="79">
@@ -12320,10 +12654,10 @@
         <v>9.83</v>
       </c>
       <c r="AG79" t="n">
-        <v>444.8</v>
+        <v>444800000</v>
       </c>
       <c r="AH79" t="n">
-        <v>444.76</v>
+        <v>444760000</v>
       </c>
       <c r="AI79" t="n">
         <v>911</v>
@@ -12384,6 +12718,12 @@
       </c>
       <c r="BB79" t="n">
         <v>893.74</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>13461</v>
       </c>
     </row>
     <row r="80">
@@ -12474,10 +12814,10 @@
         <v>349.63</v>
       </c>
       <c r="AG80" t="n">
-        <v>188.23</v>
+        <v>188230000</v>
       </c>
       <c r="AH80" t="n">
-        <v>146.56</v>
+        <v>146560000</v>
       </c>
       <c r="AI80" t="n">
         <v>235.16</v>
@@ -12532,6 +12872,12 @@
       </c>
       <c r="BB80" t="n">
         <v>161.49</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>-483076</v>
       </c>
     </row>
     <row r="81">
@@ -12625,10 +12971,10 @@
         <v>1.75</v>
       </c>
       <c r="AG81" t="n">
-        <v>956</v>
+        <v>956000000</v>
       </c>
       <c r="AH81" t="n">
-        <v>1000</v>
+        <v>1000000000</v>
       </c>
       <c r="AI81" t="n">
         <v>3690</v>
@@ -12686,6 +13032,12 @@
       </c>
       <c r="BB81" t="n">
         <v>250.54</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>-16128</v>
       </c>
     </row>
     <row r="82">
@@ -12779,10 +13131,10 @@
         <v>38.92</v>
       </c>
       <c r="AG82" t="n">
-        <v>50.4</v>
+        <v>50400000</v>
       </c>
       <c r="AH82" t="n">
-        <v>49.2</v>
+        <v>49200000</v>
       </c>
       <c r="AI82" t="n">
         <v>26.4</v>
@@ -12843,6 +13195,12 @@
       </c>
       <c r="BB82" t="n">
         <v>411.8</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>-46177</v>
       </c>
     </row>
     <row r="83">
@@ -12927,10 +13285,10 @@
         <v>23.32</v>
       </c>
       <c r="AG83" t="n">
-        <v>1000</v>
+        <v>1000000000</v>
       </c>
       <c r="AH83" t="n">
-        <v>932.5599999999999</v>
+        <v>932560000</v>
       </c>
       <c r="AI83" t="n">
         <v>1240</v>
@@ -12988,6 +13346,12 @@
       </c>
       <c r="BB83" t="n">
         <v>241.36</v>
+      </c>
+      <c r="BC83" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD83" t="n">
+        <v>-855007</v>
       </c>
     </row>
     <row r="84">
@@ -13063,10 +13427,10 @@
         <v>110.43</v>
       </c>
       <c r="AG84" t="n">
-        <v>436</v>
+        <v>436000000</v>
       </c>
       <c r="AH84" t="n">
-        <v>180.63</v>
+        <v>180630000</v>
       </c>
       <c r="AI84" t="n">
         <v>619</v>
@@ -13112,6 +13476,12 @@
       </c>
       <c r="BB84" t="n">
         <v>83.34999999999999</v>
+      </c>
+      <c r="BC84" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BD84" t="n">
+        <v>-7490738</v>
       </c>
     </row>
     <row r="85">
@@ -13205,10 +13575,10 @@
         <v>54.11</v>
       </c>
       <c r="AG85" t="n">
-        <v>3990</v>
+        <v>3990000000</v>
       </c>
       <c r="AH85" t="n">
-        <v>4110</v>
+        <v>4110000000</v>
       </c>
       <c r="AI85" t="n">
         <v>3830</v>
@@ -13238,7 +13608,7 @@
         <v>5.5</v>
       </c>
       <c r="AR85" t="n">
-        <v>41.14</v>
+        <v>41.09</v>
       </c>
       <c r="AS85" t="n">
         <v>36.55</v>
@@ -13269,6 +13639,12 @@
       </c>
       <c r="BB85" t="n">
         <v>107.74</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>-104934</v>
       </c>
     </row>
     <row r="86">
@@ -13362,10 +13738,10 @@
         <v>-8.529999999999999</v>
       </c>
       <c r="AG86" t="n">
-        <v>1870</v>
+        <v>1870000000</v>
       </c>
       <c r="AH86" t="n">
-        <v>2140</v>
+        <v>2140000000</v>
       </c>
       <c r="AI86" t="n">
         <v>65</v>
@@ -13395,7 +13771,7 @@
         <v>5.4</v>
       </c>
       <c r="AR86" t="n">
-        <v>34.91</v>
+        <v>34.92</v>
       </c>
       <c r="AS86" t="n">
         <v>20.41</v>
@@ -13426,6 +13802,12 @@
       </c>
       <c r="BB86" t="n">
         <v>47.9</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>-43000</v>
       </c>
     </row>
     <row r="87">
@@ -13519,10 +13901,10 @@
         <v>6.62</v>
       </c>
       <c r="AG87" t="n">
-        <v>489</v>
+        <v>489000000</v>
       </c>
       <c r="AH87" t="n">
-        <v>519</v>
+        <v>519000000</v>
       </c>
       <c r="AI87" t="n">
         <v>190</v>
@@ -13580,6 +13962,12 @@
       </c>
       <c r="BB87" t="n">
         <v>61.85</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>-17166</v>
       </c>
     </row>
     <row r="88">
@@ -13673,10 +14061,10 @@
         <v>-7.19</v>
       </c>
       <c r="AG88" t="n">
-        <v>1270</v>
+        <v>1270000000</v>
       </c>
       <c r="AH88" t="n">
-        <v>1320</v>
+        <v>1320000000</v>
       </c>
       <c r="AI88" t="n">
         <v>715</v>
@@ -13737,6 +14125,12 @@
       </c>
       <c r="BB88" t="n">
         <v>91.72</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>-454</v>
       </c>
     </row>
     <row r="89">
@@ -13830,10 +14224,10 @@
         <v>12.08</v>
       </c>
       <c r="AG89" t="n">
-        <v>37.63</v>
+        <v>37630000</v>
       </c>
       <c r="AH89" t="n">
-        <v>38.65</v>
+        <v>38650000</v>
       </c>
       <c r="AI89" t="n">
         <v>25.34</v>
@@ -13894,6 +14288,12 @@
       </c>
       <c r="BB89" t="n">
         <v>570.04</v>
+      </c>
+      <c r="BC89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD89" t="n">
+        <v>-828</v>
       </c>
     </row>
     <row r="90">
@@ -13984,10 +14384,10 @@
         <v>70.48999999999999</v>
       </c>
       <c r="AG90" t="n">
-        <v>439.69</v>
+        <v>439690000</v>
       </c>
       <c r="AH90" t="n">
-        <v>371.41</v>
+        <v>371410000</v>
       </c>
       <c r="AI90" t="n">
         <v>1110</v>
@@ -14045,6 +14445,12 @@
       </c>
       <c r="BB90" t="n">
         <v>196.76</v>
+      </c>
+      <c r="BC90" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD90" t="n">
+        <v>-7867235</v>
       </c>
     </row>
     <row r="91">
@@ -14135,10 +14541,10 @@
         <v>1.76</v>
       </c>
       <c r="AG91" t="n">
-        <v>363.47</v>
+        <v>363470000</v>
       </c>
       <c r="AH91" t="n">
-        <v>315.41</v>
+        <v>315410000</v>
       </c>
       <c r="AI91" t="n">
         <v>823.04</v>
@@ -14193,6 +14599,12 @@
       </c>
       <c r="BB91" t="n">
         <v>230.79</v>
+      </c>
+      <c r="BC91" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD91" t="n">
+        <v>-1170186</v>
       </c>
     </row>
     <row r="92">
@@ -14286,10 +14698,10 @@
         <v>12.19</v>
       </c>
       <c r="AG92" t="n">
-        <v>271.7</v>
+        <v>271700000</v>
       </c>
       <c r="AH92" t="n">
-        <v>306.3</v>
+        <v>306300000</v>
       </c>
       <c r="AI92" t="n">
         <v>163</v>
@@ -14350,6 +14762,12 @@
       </c>
       <c r="BB92" t="n">
         <v>669.47</v>
+      </c>
+      <c r="BC92" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD92" t="n">
+        <v>-35978</v>
       </c>
     </row>
     <row r="93">
@@ -14440,10 +14858,10 @@
         <v>-12.06</v>
       </c>
       <c r="AG93" t="n">
-        <v>145.81</v>
+        <v>145810000</v>
       </c>
       <c r="AH93" t="n">
-        <v>160.11</v>
+        <v>160110000</v>
       </c>
       <c r="AI93" t="n">
         <v>46.84</v>
@@ -14504,6 +14922,12 @@
       </c>
       <c r="BB93" t="n">
         <v>77.95999999999999</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD93" t="n">
+        <v>303594</v>
       </c>
     </row>
     <row r="94">
@@ -14597,10 +15021,10 @@
         <v>40.45</v>
       </c>
       <c r="AG94" t="n">
-        <v>684</v>
+        <v>684000000</v>
       </c>
       <c r="AH94" t="n">
-        <v>753</v>
+        <v>753000000</v>
       </c>
       <c r="AI94" t="n">
         <v>727</v>
@@ -14655,6 +15079,12 @@
       </c>
       <c r="BB94" t="n">
         <v>563.29</v>
+      </c>
+      <c r="BC94" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD94" t="n">
+        <v>-683984</v>
       </c>
     </row>
     <row r="95">
@@ -14745,10 +15175,10 @@
         <v>-6.36</v>
       </c>
       <c r="AG95" t="n">
-        <v>1810</v>
+        <v>1810000000</v>
       </c>
       <c r="AH95" t="n">
-        <v>1830</v>
+        <v>1830000000</v>
       </c>
       <c r="AI95" t="n">
         <v>1520</v>
@@ -14809,6 +15239,12 @@
       </c>
       <c r="BB95" t="n">
         <v>106.99</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>552</v>
       </c>
     </row>
     <row r="96">
@@ -14899,10 +15335,10 @@
         <v>13.39</v>
       </c>
       <c r="AG96" t="n">
-        <v>105.34</v>
+        <v>105340000</v>
       </c>
       <c r="AH96" t="n">
-        <v>100.81</v>
+        <v>100810000</v>
       </c>
       <c r="AI96" t="n">
         <v>95.03</v>
@@ -14960,6 +15396,12 @@
       </c>
       <c r="BB96" t="n">
         <v>123.76</v>
+      </c>
+      <c r="BC96" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD96" t="n">
+        <v>-94026</v>
       </c>
     </row>
     <row r="97">
@@ -15050,10 +15492,10 @@
         <v>70.98999999999999</v>
       </c>
       <c r="AG97" t="n">
-        <v>405.5</v>
+        <v>405500000</v>
       </c>
       <c r="AH97" t="n">
-        <v>427.5</v>
+        <v>427500000</v>
       </c>
       <c r="AI97" t="n">
         <v>162.4</v>
@@ -15114,6 +15556,12 @@
       </c>
       <c r="BB97" t="n">
         <v>87.34</v>
+      </c>
+      <c r="BC97" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD97" t="n">
+        <v>-95921</v>
       </c>
     </row>
     <row r="98">
@@ -15207,10 +15655,10 @@
         <v>4.34</v>
       </c>
       <c r="AG98" t="n">
-        <v>29.42</v>
+        <v>29420000</v>
       </c>
       <c r="AH98" t="n">
-        <v>30</v>
+        <v>30000000</v>
       </c>
       <c r="AI98" t="n">
         <v>38.13</v>
@@ -15271,6 +15719,12 @@
       </c>
       <c r="BB98" t="n">
         <v>287.38</v>
+      </c>
+      <c r="BC98" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD98" t="n">
+        <v>2501</v>
       </c>
     </row>
     <row r="99">
@@ -15364,10 +15818,10 @@
         <v>13.45</v>
       </c>
       <c r="AG99" t="n">
-        <v>44.8</v>
+        <v>44800000</v>
       </c>
       <c r="AH99" t="n">
-        <v>45</v>
+        <v>45000000</v>
       </c>
       <c r="AI99" t="n">
         <v>32.2</v>
@@ -15428,6 +15882,12 @@
       </c>
       <c r="BB99" t="n">
         <v>210.61</v>
+      </c>
+      <c r="BC99" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>-24000</v>
       </c>
     </row>
     <row r="100">
@@ -15521,10 +15981,10 @@
         <v>9.640000000000001</v>
       </c>
       <c r="AG100" t="n">
-        <v>468</v>
+        <v>468000000</v>
       </c>
       <c r="AH100" t="n">
-        <v>558</v>
+        <v>558000000</v>
       </c>
       <c r="AI100" t="n">
         <v>644</v>
@@ -15551,7 +16011,7 @@
         <v>5.7</v>
       </c>
       <c r="AR100" t="n">
-        <v>55.96</v>
+        <v>56.02</v>
       </c>
       <c r="AS100" t="n">
         <v>19.43</v>
@@ -15582,6 +16042,12 @@
       </c>
       <c r="BB100" t="n">
         <v>109.17</v>
+      </c>
+      <c r="BC100" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD100" t="n">
+        <v>39007130</v>
       </c>
     </row>
     <row r="101">
@@ -15675,10 +16141,10 @@
         <v>22</v>
       </c>
       <c r="AG101" t="n">
-        <v>102.2</v>
+        <v>102200000</v>
       </c>
       <c r="AH101" t="n">
-        <v>100.4</v>
+        <v>100400000</v>
       </c>
       <c r="AI101" t="n">
         <v>58</v>
@@ -15736,6 +16202,12 @@
       </c>
       <c r="BB101" t="n">
         <v>123.91</v>
+      </c>
+      <c r="BC101" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>-210102</v>
       </c>
     </row>
     <row r="102">
@@ -15826,10 +16298,10 @@
         <v>10.32</v>
       </c>
       <c r="AG102" t="n">
-        <v>45.15</v>
+        <v>45150000</v>
       </c>
       <c r="AH102" t="n">
-        <v>50.14</v>
+        <v>50140000</v>
       </c>
       <c r="AI102" t="n">
         <v>22.51</v>
@@ -15890,6 +16362,12 @@
       </c>
       <c r="BB102" t="n">
         <v>739.46</v>
+      </c>
+      <c r="BC102" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD102" t="n">
+        <v>-926</v>
       </c>
     </row>
     <row r="103">
@@ -15899,10 +16377,10 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>16.93</v>
+        <v>16.98</v>
       </c>
       <c r="C103" t="n">
-        <v>14.73</v>
+        <v>14.8</v>
       </c>
       <c r="D103" t="n">
         <v>14.62</v>
@@ -15983,10 +16461,10 @@
         <v>-40.57</v>
       </c>
       <c r="AG103" t="n">
-        <v>546</v>
+        <v>546000000</v>
       </c>
       <c r="AH103" t="n">
-        <v>587</v>
+        <v>587000000</v>
       </c>
       <c r="AI103" t="n">
         <v>231</v>
@@ -16004,7 +16482,7 @@
         <v>-27.73</v>
       </c>
       <c r="AN103" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AO103" t="n">
         <v>10</v>
@@ -16031,7 +16509,7 @@
         <v>134</v>
       </c>
       <c r="AW103" t="n">
-        <v>161.75</v>
+        <v>161.86</v>
       </c>
       <c r="AX103" t="n">
         <v>25.73</v>
@@ -16047,6 +16525,12 @@
       </c>
       <c r="BB103" t="n">
         <v>144.93</v>
+      </c>
+      <c r="BC103" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD103" t="n">
+        <v>-41880</v>
       </c>
     </row>
     <row r="104">
@@ -16134,10 +16618,10 @@
         <v>12.38</v>
       </c>
       <c r="AG104" t="n">
-        <v>46.92</v>
+        <v>46920000</v>
       </c>
       <c r="AH104" t="n">
-        <v>44.58</v>
+        <v>44580000</v>
       </c>
       <c r="AI104" t="n">
         <v>31.33</v>
@@ -16183,6 +16667,9 @@
       </c>
       <c r="BB104" t="n">
         <v>738.16</v>
+      </c>
+      <c r="BD104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -16276,10 +16763,10 @@
         <v>14</v>
       </c>
       <c r="AG105" t="n">
-        <v>391.2</v>
+        <v>391200000</v>
       </c>
       <c r="AH105" t="n">
-        <v>400.8</v>
+        <v>400800000</v>
       </c>
       <c r="AI105" t="n">
         <v>126</v>
@@ -16340,6 +16827,12 @@
       </c>
       <c r="BB105" t="n">
         <v>397.8</v>
+      </c>
+      <c r="BC105" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD105" t="n">
+        <v>-16793</v>
       </c>
     </row>
     <row r="106">
@@ -16430,10 +16923,10 @@
         <v>53.93</v>
       </c>
       <c r="AG106" t="n">
-        <v>131.94</v>
+        <v>131940000</v>
       </c>
       <c r="AH106" t="n">
-        <v>161.75</v>
+        <v>161750000</v>
       </c>
       <c r="AI106" t="n">
         <v>412</v>
@@ -16494,6 +16987,12 @@
       </c>
       <c r="BB106" t="n">
         <v>286.97</v>
+      </c>
+      <c r="BC106" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD106" t="n">
+        <v>-24724</v>
       </c>
     </row>
     <row r="107">
@@ -16581,10 +17080,10 @@
         <v>-4.81</v>
       </c>
       <c r="AG107" t="n">
-        <v>3980</v>
+        <v>3980000000</v>
       </c>
       <c r="AH107" t="n">
-        <v>4010</v>
+        <v>4010000000</v>
       </c>
       <c r="AI107" t="n">
         <v>446</v>
@@ -16645,6 +17144,12 @@
       </c>
       <c r="BB107" t="n">
         <v>13.35</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>10600</v>
       </c>
     </row>
     <row r="108">
@@ -16735,10 +17240,10 @@
         <v>-9.380000000000001</v>
       </c>
       <c r="AG108" t="n">
-        <v>289.08</v>
+        <v>289080000</v>
       </c>
       <c r="AH108" t="n">
-        <v>176.54</v>
+        <v>176540000</v>
       </c>
       <c r="AI108" t="n">
         <v>88</v>
@@ -16799,6 +17304,12 @@
       </c>
       <c r="BB108" t="n">
         <v>194.54</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>-139050</v>
       </c>
     </row>
     <row r="109">
@@ -16889,10 +17400,10 @@
         <v>15.07</v>
       </c>
       <c r="AG109" t="n">
-        <v>58.68</v>
+        <v>58680000</v>
       </c>
       <c r="AH109" t="n">
-        <v>61.1</v>
+        <v>61100000</v>
       </c>
       <c r="AI109" t="n">
         <v>250.78</v>
@@ -16922,7 +17433,7 @@
         <v>4.4</v>
       </c>
       <c r="AR109" t="n">
-        <v>59.53</v>
+        <v>59.54</v>
       </c>
       <c r="AS109" t="n">
         <v>49.29</v>
@@ -16953,6 +17464,12 @@
       </c>
       <c r="BB109" t="n">
         <v>423.59</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>-16570</v>
       </c>
     </row>
     <row r="110">
@@ -17046,10 +17563,10 @@
         <v>25.81</v>
       </c>
       <c r="AG110" t="n">
-        <v>24.56</v>
+        <v>24560000</v>
       </c>
       <c r="AH110" t="n">
-        <v>26.35</v>
+        <v>26350000</v>
       </c>
       <c r="AI110" t="n">
         <v>174.29</v>
@@ -17104,6 +17621,12 @@
       </c>
       <c r="BB110" t="n">
         <v>991.35</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>3471</v>
       </c>
     </row>
     <row r="111">
@@ -17194,10 +17717,10 @@
         <v>88.56</v>
       </c>
       <c r="AG111" t="n">
-        <v>35.41</v>
+        <v>35410000</v>
       </c>
       <c r="AH111" t="n">
-        <v>36.05</v>
+        <v>36050000</v>
       </c>
       <c r="AI111" t="n">
         <v>38.23</v>
@@ -17258,6 +17781,12 @@
       </c>
       <c r="BB111" t="n">
         <v>1587.35</v>
+      </c>
+      <c r="BC111" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD111" t="n">
+        <v>-32778</v>
       </c>
     </row>
     <row r="112">
@@ -17351,10 +17880,10 @@
         <v>26.49</v>
       </c>
       <c r="AG112" t="n">
-        <v>378</v>
+        <v>378000000</v>
       </c>
       <c r="AH112" t="n">
-        <v>462</v>
+        <v>462000000</v>
       </c>
       <c r="AI112" t="n">
         <v>159</v>
@@ -17415,6 +17944,12 @@
       </c>
       <c r="BB112" t="n">
         <v>107.9</v>
+      </c>
+      <c r="BC112" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD112" t="n">
+        <v>-353372</v>
       </c>
     </row>
     <row r="113">
@@ -17505,10 +18040,10 @@
         <v>51.25</v>
       </c>
       <c r="AG113" t="n">
-        <v>36.25</v>
+        <v>36250000</v>
       </c>
       <c r="AH113" t="n">
-        <v>36.85</v>
+        <v>36850000</v>
       </c>
       <c r="AI113" t="n">
         <v>34.63</v>
@@ -17569,6 +18104,12 @@
       </c>
       <c r="BB113" t="n">
         <v>392.68</v>
+      </c>
+      <c r="BC113" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD113" t="n">
+        <v>39533</v>
       </c>
     </row>
     <row r="114">
@@ -17659,10 +18200,10 @@
         <v>232.37</v>
       </c>
       <c r="AG114" t="n">
-        <v>78.31</v>
+        <v>78310000</v>
       </c>
       <c r="AH114" t="n">
-        <v>78.2</v>
+        <v>78200000</v>
       </c>
       <c r="AI114" t="n">
         <v>36.11</v>
@@ -17723,6 +18264,12 @@
       </c>
       <c r="BB114" t="n">
         <v>104.82</v>
+      </c>
+      <c r="BC114" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD114" t="n">
+        <v>-39812</v>
       </c>
     </row>
     <row r="115">
@@ -17813,10 +18360,10 @@
         <v>19.96</v>
       </c>
       <c r="AG115" t="n">
-        <v>107.54</v>
+        <v>107540000</v>
       </c>
       <c r="AH115" t="n">
-        <v>106.55</v>
+        <v>106550000</v>
       </c>
       <c r="AI115" t="n">
         <v>23.66</v>
@@ -17877,6 +18424,12 @@
       </c>
       <c r="BB115" t="n">
         <v>191.07</v>
+      </c>
+      <c r="BC115" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BD115" t="n">
+        <v>-57924</v>
       </c>
     </row>
     <row r="116">
@@ -17967,10 +18520,10 @@
         <v>8.949999999999999</v>
       </c>
       <c r="AG116" t="n">
-        <v>764.6</v>
+        <v>764600000</v>
       </c>
       <c r="AH116" t="n">
-        <v>805.3</v>
+        <v>805300000</v>
       </c>
       <c r="AI116" t="n">
         <v>299.3</v>
@@ -18031,6 +18584,12 @@
       </c>
       <c r="BB116" t="n">
         <v>171.77</v>
+      </c>
+      <c r="BC116" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD116" t="n">
+        <v>-174748</v>
       </c>
     </row>
     <row r="117">
@@ -18121,10 +18680,10 @@
         <v>6.06</v>
       </c>
       <c r="AG117" t="n">
-        <v>334.6</v>
+        <v>334600000</v>
       </c>
       <c r="AH117" t="n">
-        <v>360.8</v>
+        <v>360800000</v>
       </c>
       <c r="AI117" t="n">
         <v>116</v>
@@ -18185,6 +18744,12 @@
       </c>
       <c r="BB117" t="n">
         <v>55.3</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-12435</v>
       </c>
     </row>
     <row r="118">
@@ -18278,10 +18843,10 @@
         <v>35.62</v>
       </c>
       <c r="AG118" t="n">
-        <v>5850</v>
+        <v>5850000000</v>
       </c>
       <c r="AH118" t="n">
-        <v>5100</v>
+        <v>5100000000</v>
       </c>
       <c r="AI118" t="n">
         <v>11.09</v>
@@ -18429,10 +18994,10 @@
         <v>20.69</v>
       </c>
       <c r="AG119" t="n">
-        <v>140.62</v>
+        <v>140620000</v>
       </c>
       <c r="AH119" t="n">
-        <v>161.46</v>
+        <v>161460000</v>
       </c>
       <c r="AI119" t="n">
         <v>301.9</v>
@@ -18487,6 +19052,12 @@
       </c>
       <c r="BB119" t="n">
         <v>99.09</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>-31665</v>
       </c>
     </row>
     <row r="120">
@@ -18580,10 +19151,10 @@
         <v>-18.65</v>
       </c>
       <c r="AG120" t="n">
-        <v>1070</v>
+        <v>1070000000</v>
       </c>
       <c r="AH120" t="n">
-        <v>1100</v>
+        <v>1100000000</v>
       </c>
       <c r="AI120" t="n">
         <v>490</v>
@@ -18644,6 +19215,12 @@
       </c>
       <c r="BB120" t="n">
         <v>312.9</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-19338</v>
       </c>
     </row>
     <row r="121">
@@ -18737,10 +19314,10 @@
         <v>81.88</v>
       </c>
       <c r="AG121" t="n">
-        <v>619</v>
+        <v>619000000</v>
       </c>
       <c r="AH121" t="n">
-        <v>624</v>
+        <v>624000000</v>
       </c>
       <c r="AI121" t="n">
         <v>225</v>
@@ -18798,6 +19375,12 @@
       </c>
       <c r="BB121" t="n">
         <v>30.65</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-489234</v>
       </c>
     </row>
     <row r="122">
@@ -18882,10 +19465,10 @@
         <v>13.94</v>
       </c>
       <c r="AG122" t="n">
-        <v>276</v>
+        <v>276000000</v>
       </c>
       <c r="AH122" t="n">
-        <v>274</v>
+        <v>274000000</v>
       </c>
       <c r="AJ122" t="n">
         <v>-1700</v>
@@ -18937,6 +19520,12 @@
       </c>
       <c r="BB122" t="n">
         <v>925.09</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -19027,10 +19616,10 @@
         <v>8.51</v>
       </c>
       <c r="AG123" t="n">
-        <v>558</v>
+        <v>558000000</v>
       </c>
       <c r="AH123" t="n">
-        <v>552</v>
+        <v>552000000</v>
       </c>
       <c r="AI123" t="n">
         <v>239</v>
@@ -19085,6 +19674,12 @@
       </c>
       <c r="BB123" t="n">
         <v>43.03</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>3335</v>
       </c>
     </row>
     <row r="124">
@@ -19172,10 +19767,10 @@
         <v>-49.15</v>
       </c>
       <c r="AG124" t="n">
-        <v>11.14</v>
+        <v>11140000</v>
       </c>
       <c r="AH124" t="n">
-        <v>10.65</v>
+        <v>10650000</v>
       </c>
       <c r="AI124" t="n">
         <v>2.24</v>
@@ -19233,6 +19828,12 @@
       </c>
       <c r="BB124" t="n">
         <v>85.28</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>936</v>
       </c>
     </row>
     <row r="125">
@@ -19326,10 +19927,10 @@
         <v>17.77</v>
       </c>
       <c r="AG125" t="n">
-        <v>1260</v>
+        <v>1260000000</v>
       </c>
       <c r="AH125" t="n">
-        <v>1260</v>
+        <v>1260000000</v>
       </c>
       <c r="AI125" t="n">
         <v>1020</v>
@@ -19359,7 +19960,7 @@
         <v>5.6</v>
       </c>
       <c r="AR125" t="n">
-        <v>58.09</v>
+        <v>58.1</v>
       </c>
       <c r="AS125" t="n">
         <v>1.7</v>
@@ -19390,6 +19991,12 @@
       </c>
       <c r="BB125" t="n">
         <v>147.68</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-104261</v>
       </c>
     </row>
     <row r="126">
@@ -19483,10 +20090,10 @@
         <v>86.63</v>
       </c>
       <c r="AG126" t="n">
-        <v>871</v>
+        <v>871000000</v>
       </c>
       <c r="AH126" t="n">
-        <v>857</v>
+        <v>857000000</v>
       </c>
       <c r="AI126" t="n">
         <v>419</v>
@@ -19547,6 +20154,12 @@
       </c>
       <c r="BB126" t="n">
         <v>144.16</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-41352</v>
       </c>
     </row>
     <row r="127">
@@ -19616,10 +20229,10 @@
         <v>-39.24</v>
       </c>
       <c r="AG127" t="n">
-        <v>366.48</v>
+        <v>366480000</v>
       </c>
       <c r="AH127" t="n">
-        <v>104.84</v>
+        <v>104840000</v>
       </c>
       <c r="AI127" t="n">
         <v>71.26000000000001</v>
@@ -19671,6 +20284,12 @@
       </c>
       <c r="BB127" t="n">
         <v>22.27</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>233658</v>
       </c>
     </row>
     <row r="128">
@@ -19764,10 +20383,10 @@
         <v>239.45</v>
       </c>
       <c r="AG128" t="n">
-        <v>973</v>
+        <v>973000000</v>
       </c>
       <c r="AH128" t="n">
-        <v>1450</v>
+        <v>1450000000</v>
       </c>
       <c r="AI128" t="n">
         <v>334</v>
@@ -19828,6 +20447,12 @@
       </c>
       <c r="BB128" t="n">
         <v>84.29000000000001</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>-582334</v>
       </c>
     </row>
     <row r="129">
@@ -19918,10 +20543,10 @@
         <v>9.66</v>
       </c>
       <c r="AG129" t="n">
-        <v>12230</v>
+        <v>12230000000</v>
       </c>
       <c r="AH129" t="n">
-        <v>13160</v>
+        <v>13160000000</v>
       </c>
       <c r="AI129" t="n">
         <v>28640</v>
@@ -19979,6 +20604,12 @@
       </c>
       <c r="BB129" t="n">
         <v>342.87</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>-673200</v>
       </c>
     </row>
     <row r="130">
@@ -20069,10 +20700,10 @@
         <v>675</v>
       </c>
       <c r="AG130" t="n">
-        <v>4210</v>
+        <v>4210000000</v>
       </c>
       <c r="AH130" t="n">
-        <v>3810</v>
+        <v>3810000000</v>
       </c>
       <c r="AI130" t="n">
         <v>240</v>
@@ -20096,7 +20727,7 @@
         <v>1.7</v>
       </c>
       <c r="AR130" t="n">
-        <v>25.49</v>
+        <v>25.22</v>
       </c>
       <c r="AS130" t="n">
         <v>-23.47</v>
@@ -20127,6 +20758,12 @@
       </c>
       <c r="BB130" t="n">
         <v>2.87</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>-563612</v>
       </c>
     </row>
     <row r="131">
@@ -20217,10 +20854,10 @@
         <v>19</v>
       </c>
       <c r="AG131" t="n">
-        <v>193.62</v>
+        <v>193620000</v>
       </c>
       <c r="AH131" t="n">
-        <v>193.04</v>
+        <v>193040000</v>
       </c>
       <c r="AI131" t="n">
         <v>172.52</v>
@@ -20281,6 +20918,12 @@
       </c>
       <c r="BB131" t="n">
         <v>276.93</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>-359736</v>
       </c>
     </row>
     <row r="132">
@@ -20353,10 +20996,10 @@
         <v>15.23</v>
       </c>
       <c r="AG132" t="n">
-        <v>317.6</v>
+        <v>317600000</v>
       </c>
       <c r="AH132" t="n">
-        <v>358.1</v>
+        <v>358100000</v>
       </c>
       <c r="AI132" t="n">
         <v>3640</v>
@@ -20414,6 +21057,12 @@
       </c>
       <c r="BB132" t="n">
         <v>937.98</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>-3025</v>
       </c>
     </row>
     <row r="133">
@@ -20507,10 +21156,10 @@
         <v>37.5</v>
       </c>
       <c r="AG133" t="n">
-        <v>95.5</v>
+        <v>95500000</v>
       </c>
       <c r="AH133" t="n">
-        <v>111.26</v>
+        <v>111260000</v>
       </c>
       <c r="AI133" t="n">
         <v>73</v>
@@ -20568,6 +21217,12 @@
       </c>
       <c r="BB133" t="n">
         <v>158.65</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>-123525</v>
       </c>
     </row>
     <row r="134">
@@ -20661,10 +21316,10 @@
         <v>-14.37</v>
       </c>
       <c r="AG134" t="n">
-        <v>990</v>
+        <v>990000000</v>
       </c>
       <c r="AH134" t="n">
-        <v>1020</v>
+        <v>1020000000</v>
       </c>
       <c r="AI134" t="n">
         <v>562</v>
@@ -20722,6 +21377,12 @@
       </c>
       <c r="BB134" t="n">
         <v>302.47</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>-5347</v>
       </c>
     </row>
     <row r="135">
@@ -20815,10 +21476,10 @@
         <v>-70.41</v>
       </c>
       <c r="AG135" t="n">
-        <v>174.59</v>
+        <v>174590000</v>
       </c>
       <c r="AH135" t="n">
-        <v>174.82</v>
+        <v>174820000</v>
       </c>
       <c r="AI135" t="n">
         <v>8</v>
@@ -20879,6 +21540,9 @@
       </c>
       <c r="BB135" t="n">
         <v>13.05</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="136">
@@ -20972,10 +21636,10 @@
         <v>21.92</v>
       </c>
       <c r="AG136" t="n">
-        <v>238</v>
+        <v>238000000</v>
       </c>
       <c r="AH136" t="n">
-        <v>277</v>
+        <v>277000000</v>
       </c>
       <c r="AI136" t="n">
         <v>185</v>
@@ -21030,6 +21694,12 @@
       </c>
       <c r="BB136" t="n">
         <v>305.63</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-3570</v>
       </c>
     </row>
     <row r="137">
@@ -21120,10 +21790,10 @@
         <v>-3.27</v>
       </c>
       <c r="AG137" t="n">
-        <v>321.4</v>
+        <v>321400000</v>
       </c>
       <c r="AH137" t="n">
-        <v>341.55</v>
+        <v>341550000</v>
       </c>
       <c r="AI137" t="n">
         <v>186</v>
@@ -21184,6 +21854,12 @@
       </c>
       <c r="BB137" t="n">
         <v>207.66</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-15317</v>
       </c>
     </row>
     <row r="138">
@@ -21256,10 +21932,10 @@
         <v>26.53</v>
       </c>
       <c r="AG138" t="n">
-        <v>918.78</v>
+        <v>918780000</v>
       </c>
       <c r="AH138" t="n">
-        <v>878.63</v>
+        <v>878630000</v>
       </c>
       <c r="AI138" t="n">
         <v>351</v>
@@ -21311,6 +21987,12 @@
       </c>
       <c r="BB138" t="n">
         <v>104.42</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>-598603</v>
       </c>
     </row>
     <row r="139">
@@ -21401,10 +22083,10 @@
         <v>-59.33</v>
       </c>
       <c r="AG139" t="n">
-        <v>1320</v>
+        <v>1320000000</v>
       </c>
       <c r="AH139" t="n">
-        <v>1320</v>
+        <v>1320000000</v>
       </c>
       <c r="AI139" t="n">
         <v>795</v>
@@ -21465,6 +22147,12 @@
       </c>
       <c r="BB139" t="n">
         <v>56.68</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>-134889</v>
       </c>
     </row>
     <row r="140">
@@ -21558,10 +22246,10 @@
         <v>9.81</v>
       </c>
       <c r="AG140" t="n">
-        <v>53.5</v>
+        <v>53500000</v>
       </c>
       <c r="AH140" t="n">
-        <v>54.1</v>
+        <v>54100000</v>
       </c>
       <c r="AI140" t="n">
         <v>34.2</v>
@@ -21622,6 +22310,12 @@
       </c>
       <c r="BB140" t="n">
         <v>439.07</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>-1169</v>
       </c>
     </row>
     <row r="141">
@@ -21709,10 +22403,10 @@
         <v>20.42</v>
       </c>
       <c r="AG141" t="n">
-        <v>53.19</v>
+        <v>53190000</v>
       </c>
       <c r="AH141" t="n">
-        <v>48.06</v>
+        <v>48060000</v>
       </c>
       <c r="AI141" t="n">
         <v>514.71</v>
@@ -21770,6 +22464,12 @@
       </c>
       <c r="BB141" t="n">
         <v>236.46</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>-24974</v>
       </c>
     </row>
     <row r="142">
@@ -21863,10 +22563,10 @@
         <v>33.41</v>
       </c>
       <c r="AG142" t="n">
-        <v>406</v>
+        <v>406000000</v>
       </c>
       <c r="AH142" t="n">
-        <v>421</v>
+        <v>421000000</v>
       </c>
       <c r="AI142" t="n">
         <v>91</v>
@@ -21927,6 +22627,12 @@
       </c>
       <c r="BB142" t="n">
         <v>227.73</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="143">
@@ -21996,10 +22702,10 @@
         <v>15.16</v>
       </c>
       <c r="AG143" t="n">
-        <v>443.86</v>
+        <v>443860000</v>
       </c>
       <c r="AH143" t="n">
-        <v>405.2</v>
+        <v>405200000</v>
       </c>
       <c r="AI143" t="n">
         <v>124</v>
@@ -22057,6 +22763,12 @@
       </c>
       <c r="BB143" t="n">
         <v>86.73999999999999</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>803643</v>
       </c>
     </row>
     <row r="144">
@@ -22147,10 +22859,10 @@
         <v>28.35</v>
       </c>
       <c r="AG144" t="n">
-        <v>948.6799999999999</v>
+        <v>948680000</v>
       </c>
       <c r="AH144" t="n">
-        <v>912.27</v>
+        <v>912270000</v>
       </c>
       <c r="AI144" t="n">
         <v>1880</v>
@@ -22211,6 +22923,12 @@
       </c>
       <c r="BB144" t="n">
         <v>237.49</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>-25775</v>
       </c>
     </row>
     <row r="145">
@@ -22301,10 +23019,10 @@
         <v>44.22</v>
       </c>
       <c r="AG145" t="n">
-        <v>200.7</v>
+        <v>200700000</v>
       </c>
       <c r="AH145" t="n">
-        <v>223.96</v>
+        <v>223960000</v>
       </c>
       <c r="AI145" t="n">
         <v>255.14</v>
@@ -22365,6 +23083,12 @@
       </c>
       <c r="BB145" t="n">
         <v>124.75</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>-102759</v>
       </c>
     </row>
     <row r="146">
@@ -22458,10 +23182,10 @@
         <v>-2.9</v>
       </c>
       <c r="AG146" t="n">
-        <v>4530</v>
+        <v>4530000000</v>
       </c>
       <c r="AH146" t="n">
-        <v>4120</v>
+        <v>4120000000</v>
       </c>
       <c r="AI146" t="n">
         <v>2390</v>
@@ -22491,7 +23215,7 @@
         <v>1.8</v>
       </c>
       <c r="AR146" t="n">
-        <v>54.73</v>
+        <v>54.74</v>
       </c>
       <c r="AS146" t="n">
         <v>120.83</v>
@@ -22522,6 +23246,12 @@
       </c>
       <c r="BB146" t="n">
         <v>101.05</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>108794</v>
       </c>
     </row>
     <row r="147">
@@ -22615,10 +23345,10 @@
         <v>125.88</v>
       </c>
       <c r="AG147" t="n">
-        <v>277</v>
+        <v>277000000</v>
       </c>
       <c r="AH147" t="n">
-        <v>283</v>
+        <v>283000000</v>
       </c>
       <c r="AI147" t="n">
         <v>2060</v>
@@ -22645,7 +23375,7 @@
         <v>9</v>
       </c>
       <c r="AR147" t="n">
-        <v>43.46</v>
+        <v>43.44</v>
       </c>
       <c r="AS147" t="n">
         <v>-29.67</v>
@@ -22676,6 +23406,12 @@
       </c>
       <c r="BB147" t="n">
         <v>318.13</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>583</v>
       </c>
     </row>
     <row r="148">
@@ -22766,10 +23502,10 @@
         <v>17.61</v>
       </c>
       <c r="AG148" t="n">
-        <v>362.7</v>
+        <v>362700000</v>
       </c>
       <c r="AH148" t="n">
-        <v>362</v>
+        <v>362000000</v>
       </c>
       <c r="AI148" t="n">
         <v>839.3</v>
@@ -22830,6 +23566,12 @@
       </c>
       <c r="BB148" t="n">
         <v>382.29</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>-11498</v>
       </c>
     </row>
     <row r="149">
@@ -22923,10 +23665,10 @@
         <v>2.55</v>
       </c>
       <c r="AG149" t="n">
-        <v>75.61</v>
+        <v>75610000</v>
       </c>
       <c r="AH149" t="n">
-        <v>81.06999999999999</v>
+        <v>81070000</v>
       </c>
       <c r="AI149" t="n">
         <v>149.6</v>
@@ -22981,6 +23723,12 @@
       </c>
       <c r="BB149" t="n">
         <v>191.57</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>-5315</v>
       </c>
     </row>
     <row r="150">
@@ -23065,10 +23813,10 @@
         <v>2.4</v>
       </c>
       <c r="AG150" t="n">
-        <v>121.93</v>
+        <v>121930000</v>
       </c>
       <c r="AH150" t="n">
-        <v>129.44</v>
+        <v>129440000</v>
       </c>
       <c r="AI150" t="n">
         <v>70.42</v>
@@ -23126,6 +23874,12 @@
       </c>
       <c r="BB150" t="n">
         <v>143.49</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>-17253</v>
       </c>
     </row>
     <row r="151">
@@ -23219,10 +23973,10 @@
         <v>29.92</v>
       </c>
       <c r="AG151" t="n">
-        <v>110.9</v>
+        <v>110900000</v>
       </c>
       <c r="AH151" t="n">
-        <v>144.4</v>
+        <v>144400000</v>
       </c>
       <c r="AI151" t="n">
         <v>138</v>
@@ -23283,6 +24037,12 @@
       </c>
       <c r="BB151" t="n">
         <v>297.24</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>-866</v>
       </c>
     </row>
     <row r="152">
@@ -23295,10 +24055,10 @@
         <v>5.06</v>
       </c>
       <c r="C152" t="n">
-        <v>6.05</v>
+        <v>6.07</v>
       </c>
       <c r="D152" t="n">
-        <v>7.1</v>
+        <v>7.13</v>
       </c>
       <c r="H152" t="n">
         <v>13.12</v>
@@ -23376,10 +24136,10 @@
         <v>-41.27</v>
       </c>
       <c r="AG152" t="n">
-        <v>654.1</v>
+        <v>654100000</v>
       </c>
       <c r="AH152" t="n">
-        <v>699.6</v>
+        <v>699600000</v>
       </c>
       <c r="AI152" t="n">
         <v>128</v>
@@ -23430,16 +24190,22 @@
         <v>14.32</v>
       </c>
       <c r="AY152" t="n">
-        <v>7.97</v>
+        <v>8.01</v>
       </c>
       <c r="AZ152" t="n">
-        <v>23.6</v>
+        <v>23.78</v>
       </c>
       <c r="BA152" t="n">
         <v>-10.56</v>
       </c>
       <c r="BB152" t="n">
         <v>140.47</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>-69003</v>
       </c>
     </row>
     <row r="153">
@@ -23533,10 +24299,10 @@
         <v>44.01</v>
       </c>
       <c r="AG153" t="n">
-        <v>2430</v>
+        <v>2430000000</v>
       </c>
       <c r="AH153" t="n">
-        <v>2660</v>
+        <v>2660000000</v>
       </c>
       <c r="AI153" t="n">
         <v>1410</v>
@@ -23597,6 +24363,12 @@
       </c>
       <c r="BB153" t="n">
         <v>267.28</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>-259340</v>
       </c>
     </row>
     <row r="154">
@@ -23690,10 +24462,10 @@
         <v>-6.87</v>
       </c>
       <c r="AG154" t="n">
-        <v>173</v>
+        <v>173000000</v>
       </c>
       <c r="AH154" t="n">
-        <v>182</v>
+        <v>182000000</v>
       </c>
       <c r="AI154" t="n">
         <v>227</v>
@@ -23754,6 +24526,12 @@
       </c>
       <c r="BB154" t="n">
         <v>322.04</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>-7630</v>
       </c>
     </row>
     <row r="155">
@@ -23847,10 +24625,10 @@
         <v>14.96</v>
       </c>
       <c r="AG155" t="n">
-        <v>1320</v>
+        <v>1320000000</v>
       </c>
       <c r="AH155" t="n">
-        <v>1400</v>
+        <v>1400000000</v>
       </c>
       <c r="AI155" t="n">
         <v>310.17</v>
@@ -23911,6 +24689,12 @@
       </c>
       <c r="BB155" t="n">
         <v>167.36</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>-22220</v>
       </c>
     </row>
     <row r="156">
@@ -23998,10 +24782,10 @@
         <v>-2.07</v>
       </c>
       <c r="AG156" t="n">
-        <v>53.19</v>
+        <v>53190000</v>
       </c>
       <c r="AH156" t="n">
-        <v>61.18</v>
+        <v>61180000</v>
       </c>
       <c r="AI156" t="n">
         <v>27.16</v>
@@ -24062,6 +24846,12 @@
       </c>
       <c r="BB156" t="n">
         <v>79.55</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>38177</v>
       </c>
     </row>
     <row r="157">
@@ -24155,10 +24945,10 @@
         <v>-13.13</v>
       </c>
       <c r="AG157" t="n">
-        <v>162.61</v>
+        <v>162610000</v>
       </c>
       <c r="AH157" t="n">
-        <v>163.21</v>
+        <v>163210000</v>
       </c>
       <c r="AI157" t="n">
         <v>28.56</v>
@@ -24213,6 +25003,12 @@
       </c>
       <c r="BB157" t="n">
         <v>65.78</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>-336694</v>
       </c>
     </row>
     <row r="158">
@@ -24306,10 +25102,10 @@
         <v>-5.82</v>
       </c>
       <c r="AG158" t="n">
-        <v>4310</v>
+        <v>4310000000</v>
       </c>
       <c r="AH158" t="n">
-        <v>4350</v>
+        <v>4350000000</v>
       </c>
       <c r="AI158" t="n">
         <v>266</v>
@@ -24370,6 +25166,12 @@
       </c>
       <c r="BB158" t="n">
         <v>87.87</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>-978198</v>
       </c>
     </row>
     <row r="159">
@@ -24463,10 +25265,10 @@
         <v>6.04</v>
       </c>
       <c r="AG159" t="n">
-        <v>655</v>
+        <v>655000000</v>
       </c>
       <c r="AH159" t="n">
-        <v>727</v>
+        <v>727000000</v>
       </c>
       <c r="AI159" t="n">
         <v>175</v>
@@ -24527,6 +25329,12 @@
       </c>
       <c r="BB159" t="n">
         <v>61.14</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>3207</v>
       </c>
     </row>
     <row r="160">
@@ -24620,10 +25428,10 @@
         <v>10.54</v>
       </c>
       <c r="AG160" t="n">
-        <v>53.59</v>
+        <v>53590000</v>
       </c>
       <c r="AH160" t="n">
-        <v>59.92</v>
+        <v>59920000</v>
       </c>
       <c r="AI160" t="n">
         <v>66.2</v>
@@ -24684,6 +25492,12 @@
       </c>
       <c r="BB160" t="n">
         <v>123.19</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>-51593</v>
       </c>
     </row>
     <row r="161">
@@ -24771,10 +25585,10 @@
         <v>-80.09</v>
       </c>
       <c r="AG161" t="n">
-        <v>19.93</v>
+        <v>19930000</v>
       </c>
       <c r="AH161" t="n">
-        <v>14.99</v>
+        <v>14990000</v>
       </c>
       <c r="AI161" t="n">
         <v>19.2</v>
@@ -24835,6 +25649,12 @@
       </c>
       <c r="BB161" t="n">
         <v>139.01</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>2359</v>
       </c>
     </row>
     <row r="162">
@@ -24928,10 +25748,10 @@
         <v>-12.01</v>
       </c>
       <c r="AG162" t="n">
-        <v>399.75</v>
+        <v>399750000</v>
       </c>
       <c r="AH162" t="n">
-        <v>403.84</v>
+        <v>403840000</v>
       </c>
       <c r="AI162" t="n">
         <v>77.5</v>
@@ -24992,6 +25812,12 @@
       </c>
       <c r="BB162" t="n">
         <v>19.65</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>-429156</v>
       </c>
     </row>
     <row r="163">
@@ -25082,10 +25908,10 @@
         <v>81.89</v>
       </c>
       <c r="AG163" t="n">
-        <v>24.82</v>
+        <v>24820000</v>
       </c>
       <c r="AH163" t="n">
-        <v>24.99</v>
+        <v>24990000</v>
       </c>
       <c r="AI163" t="n">
         <v>30.11</v>
@@ -25146,6 +25972,12 @@
       </c>
       <c r="BB163" t="n">
         <v>396.02</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>-2293</v>
       </c>
     </row>
     <row r="164">
@@ -25230,10 +26062,10 @@
         <v>109.34</v>
       </c>
       <c r="AG164" t="n">
-        <v>74.59999999999999</v>
+        <v>74600000</v>
       </c>
       <c r="AH164" t="n">
-        <v>68.3</v>
+        <v>68300000</v>
       </c>
       <c r="AI164" t="n">
         <v>170.2</v>
@@ -25294,6 +26126,12 @@
       </c>
       <c r="BB164" t="n">
         <v>919.4</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>115195</v>
       </c>
     </row>
     <row r="165">
@@ -25387,10 +26225,10 @@
         <v>62.32</v>
       </c>
       <c r="AG165" t="n">
-        <v>899.3</v>
+        <v>899300000</v>
       </c>
       <c r="AH165" t="n">
-        <v>904.62</v>
+        <v>904620000</v>
       </c>
       <c r="AI165" t="n">
         <v>649</v>
@@ -25451,6 +26289,12 @@
       </c>
       <c r="BB165" t="n">
         <v>1137.82</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>-13584</v>
       </c>
     </row>
     <row r="166">
@@ -25544,10 +26388,10 @@
         <v>1.32</v>
       </c>
       <c r="AG166" t="n">
-        <v>560</v>
+        <v>560000000</v>
       </c>
       <c r="AH166" t="n">
-        <v>631</v>
+        <v>631000000</v>
       </c>
       <c r="AI166" t="n">
         <v>262</v>
@@ -25602,6 +26446,12 @@
       </c>
       <c r="BB166" t="n">
         <v>194.1</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>-12500</v>
       </c>
     </row>
     <row r="167">
@@ -25692,10 +26542,10 @@
         <v>44.36</v>
       </c>
       <c r="AG167" t="n">
-        <v>1260</v>
+        <v>1260000000</v>
       </c>
       <c r="AH167" t="n">
-        <v>1360</v>
+        <v>1360000000</v>
       </c>
       <c r="AI167" t="n">
         <v>386.38</v>
@@ -25756,6 +26606,12 @@
       </c>
       <c r="BB167" t="n">
         <v>269.23</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>-148822</v>
       </c>
     </row>
     <row r="168">
@@ -25846,10 +26702,10 @@
         <v>-5.55</v>
       </c>
       <c r="AG168" t="n">
-        <v>138.24</v>
+        <v>138240000</v>
       </c>
       <c r="AH168" t="n">
-        <v>140.67</v>
+        <v>140670000</v>
       </c>
       <c r="AI168" t="n">
         <v>143.63</v>
@@ -25910,6 +26766,12 @@
       </c>
       <c r="BB168" t="n">
         <v>106.32</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>-29163</v>
       </c>
     </row>
     <row r="169">
@@ -26003,10 +26865,10 @@
         <v>-21.87</v>
       </c>
       <c r="AG169" t="n">
-        <v>119.07</v>
+        <v>119070000</v>
       </c>
       <c r="AH169" t="n">
-        <v>128.02</v>
+        <v>128020000</v>
       </c>
       <c r="AI169" t="n">
         <v>91.23</v>
@@ -26067,6 +26929,12 @@
       </c>
       <c r="BB169" t="n">
         <v>95.98</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>-316339</v>
       </c>
     </row>
     <row r="170">
@@ -26151,10 +27019,10 @@
         <v>86.72</v>
       </c>
       <c r="AG170" t="n">
-        <v>1010</v>
+        <v>1010000000</v>
       </c>
       <c r="AH170" t="n">
-        <v>915.85</v>
+        <v>915850000</v>
       </c>
       <c r="AI170" t="n">
         <v>9.880000000000001</v>
@@ -26172,7 +27040,7 @@
         <v>138.9</v>
       </c>
       <c r="AN170" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="AO170" t="n">
         <v>27.8</v>
@@ -26212,6 +27080,9 @@
       </c>
       <c r="BB170" t="n">
         <v>13.84</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>449412</v>
       </c>
     </row>
     <row r="171">
@@ -26302,10 +27173,10 @@
         <v>11.12</v>
       </c>
       <c r="AG171" t="n">
-        <v>231.84</v>
+        <v>231840000</v>
       </c>
       <c r="AH171" t="n">
-        <v>231.56</v>
+        <v>231560000</v>
       </c>
       <c r="AI171" t="n">
         <v>163.93</v>
@@ -26360,6 +27231,12 @@
       </c>
       <c r="BB171" t="n">
         <v>171.13</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>-41122</v>
       </c>
     </row>
     <row r="172">
@@ -26453,10 +27330,10 @@
         <v>-1.34</v>
       </c>
       <c r="AG172" t="n">
-        <v>276.5</v>
+        <v>276500000</v>
       </c>
       <c r="AH172" t="n">
-        <v>281.1</v>
+        <v>281100000</v>
       </c>
       <c r="AI172" t="n">
         <v>63</v>
@@ -26517,6 +27394,12 @@
       </c>
       <c r="BB172" t="n">
         <v>21.81</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>-6496</v>
       </c>
     </row>
     <row r="173">
@@ -26610,10 +27493,10 @@
         <v>20.53</v>
       </c>
       <c r="AG173" t="n">
-        <v>906</v>
+        <v>906000000</v>
       </c>
       <c r="AH173" t="n">
-        <v>971</v>
+        <v>971000000</v>
       </c>
       <c r="AI173" t="n">
         <v>615</v>
@@ -26671,6 +27554,12 @@
       </c>
       <c r="BB173" t="n">
         <v>567.75</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>-104708</v>
       </c>
     </row>
     <row r="174">
@@ -26764,10 +27653,10 @@
         <v>0.25</v>
       </c>
       <c r="AG174" t="n">
-        <v>273.6</v>
+        <v>273600000</v>
       </c>
       <c r="AH174" t="n">
-        <v>325.8</v>
+        <v>325800000</v>
       </c>
       <c r="AI174" t="n">
         <v>249</v>
@@ -26822,6 +27711,12 @@
       </c>
       <c r="BB174" t="n">
         <v>334.97</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>-59</v>
       </c>
     </row>
     <row r="175">
@@ -26915,10 +27810,10 @@
         <v>-2.72</v>
       </c>
       <c r="AG175" t="n">
-        <v>497.98</v>
+        <v>497980000</v>
       </c>
       <c r="AH175" t="n">
-        <v>502.48</v>
+        <v>502480000</v>
       </c>
       <c r="AI175" t="n">
         <v>222.68</v>
@@ -27072,10 +27967,10 @@
         <v>71.26000000000001</v>
       </c>
       <c r="AG176" t="n">
-        <v>124.1</v>
+        <v>124100000</v>
       </c>
       <c r="AH176" t="n">
-        <v>142.2</v>
+        <v>142200000</v>
       </c>
       <c r="AI176" t="n">
         <v>247</v>
@@ -27133,6 +28028,12 @@
       </c>
       <c r="BB176" t="n">
         <v>887.29</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>-16507</v>
       </c>
     </row>
     <row r="177">
@@ -27226,10 +28127,10 @@
         <v>28.8</v>
       </c>
       <c r="AG177" t="n">
-        <v>179.9</v>
+        <v>179900000</v>
       </c>
       <c r="AH177" t="n">
-        <v>184.7</v>
+        <v>184700000</v>
       </c>
       <c r="AI177" t="n">
         <v>233</v>
@@ -27287,6 +28188,12 @@
       </c>
       <c r="BB177" t="n">
         <v>465.3</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>17069</v>
       </c>
     </row>
     <row r="178">
@@ -27371,10 +28278,10 @@
         <v>26.75</v>
       </c>
       <c r="AG178" t="n">
-        <v>81.25</v>
+        <v>81250000</v>
       </c>
       <c r="AH178" t="n">
-        <v>68.63</v>
+        <v>68630000</v>
       </c>
       <c r="AI178" t="n">
         <v>564.39</v>
@@ -27429,6 +28336,12 @@
       </c>
       <c r="BB178" t="n">
         <v>376.34</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>-38784</v>
       </c>
     </row>
     <row r="179">
@@ -27522,10 +28435,10 @@
         <v>48.39</v>
       </c>
       <c r="AG179" t="n">
-        <v>1290</v>
+        <v>1290000000</v>
       </c>
       <c r="AH179" t="n">
-        <v>1330</v>
+        <v>1330000000</v>
       </c>
       <c r="AI179" t="n">
         <v>496</v>
@@ -27586,6 +28499,12 @@
       </c>
       <c r="BB179" t="n">
         <v>92.59999999999999</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>108661</v>
       </c>
     </row>
     <row r="180">
@@ -27679,10 +28598,10 @@
         <v>8.41</v>
       </c>
       <c r="AG180" t="n">
-        <v>50.7</v>
+        <v>50700000</v>
       </c>
       <c r="AH180" t="n">
-        <v>51.34</v>
+        <v>51340000</v>
       </c>
       <c r="AI180" t="n">
         <v>280</v>
@@ -27743,6 +28662,12 @@
       </c>
       <c r="BB180" t="n">
         <v>1839.71</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
@@ -27836,10 +28761,10 @@
         <v>5.91</v>
       </c>
       <c r="AG181" t="n">
-        <v>2570</v>
+        <v>2570000000</v>
       </c>
       <c r="AH181" t="n">
-        <v>2700</v>
+        <v>2700000000</v>
       </c>
       <c r="AI181" t="n">
         <v>25140</v>
@@ -27897,6 +28822,12 @@
       </c>
       <c r="BB181" t="n">
         <v>673.3099999999999</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>-58486</v>
       </c>
     </row>
     <row r="182">
@@ -27990,10 +28921,10 @@
         <v>14.38</v>
       </c>
       <c r="AG182" t="n">
-        <v>282.5</v>
+        <v>282500000</v>
       </c>
       <c r="AH182" t="n">
-        <v>291.2</v>
+        <v>291200000</v>
       </c>
       <c r="AJ182" t="n">
         <v>-1290</v>
@@ -28014,7 +28945,7 @@
         <v>9.4</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ182" t="n">
         <v>1.4</v>
@@ -28042,6 +28973,9 @@
       </c>
       <c r="BB182" t="n">
         <v>63.74</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>-5000</v>
       </c>
     </row>
     <row r="183">
@@ -28135,10 +29069,10 @@
         <v>-28.07</v>
       </c>
       <c r="AG183" t="n">
-        <v>541.3</v>
+        <v>541300000</v>
       </c>
       <c r="AH183" t="n">
-        <v>567.6</v>
+        <v>567600000</v>
       </c>
       <c r="AI183" t="n">
         <v>217</v>
@@ -28199,6 +29133,12 @@
       </c>
       <c r="BB183" t="n">
         <v>162.65</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>-24174</v>
       </c>
     </row>
     <row r="184">
@@ -28289,10 +29229,10 @@
         <v>31.28</v>
       </c>
       <c r="AG184" t="n">
-        <v>1970</v>
+        <v>1970000000</v>
       </c>
       <c r="AH184" t="n">
-        <v>2130</v>
+        <v>2130000000</v>
       </c>
       <c r="AI184" t="n">
         <v>135.8</v>
@@ -28353,6 +29293,12 @@
       </c>
       <c r="BB184" t="n">
         <v>44.57</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>2480</v>
       </c>
     </row>
     <row r="185">
@@ -28446,10 +29392,10 @@
         <v>-6.53</v>
       </c>
       <c r="AG185" t="n">
-        <v>1680</v>
+        <v>1680000000</v>
       </c>
       <c r="AH185" t="n">
-        <v>1800</v>
+        <v>1800000000</v>
       </c>
       <c r="AI185" t="n">
         <v>62</v>
@@ -28507,6 +29453,12 @@
       </c>
       <c r="BB185" t="n">
         <v>70.09999999999999</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>1500</v>
       </c>
     </row>
     <row r="186">
@@ -28600,10 +29552,10 @@
         <v>35.37</v>
       </c>
       <c r="AG186" t="n">
-        <v>53.8</v>
+        <v>53800000</v>
       </c>
       <c r="AH186" t="n">
-        <v>52.8</v>
+        <v>52800000</v>
       </c>
       <c r="AI186" t="n">
         <v>24.8</v>
@@ -28664,6 +29616,12 @@
       </c>
       <c r="BB186" t="n">
         <v>181.18</v>
+      </c>
+      <c r="BC186" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>-35572</v>
       </c>
     </row>
     <row r="187">
@@ -28745,10 +29703,10 @@
         <v>70.04000000000001</v>
       </c>
       <c r="AG187" t="n">
-        <v>170.13</v>
+        <v>170130000</v>
       </c>
       <c r="AH187" t="n">
-        <v>193.45</v>
+        <v>193450000</v>
       </c>
       <c r="AI187" t="n">
         <v>41.48</v>
@@ -28806,6 +29764,12 @@
       </c>
       <c r="BB187" t="n">
         <v>48.99</v>
+      </c>
+      <c r="BC187" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>624</v>
       </c>
     </row>
     <row r="188">
@@ -28896,10 +29860,10 @@
         <v>22.43</v>
       </c>
       <c r="AG188" t="n">
-        <v>48.31</v>
+        <v>48310000</v>
       </c>
       <c r="AH188" t="n">
-        <v>48.36</v>
+        <v>48360000</v>
       </c>
       <c r="AI188" t="n">
         <v>208.87</v>
@@ -28929,7 +29893,7 @@
         <v>14.9</v>
       </c>
       <c r="AR188" t="n">
-        <v>34.75</v>
+        <v>34.72</v>
       </c>
       <c r="AS188" t="n">
         <v>6.52</v>
@@ -28960,6 +29924,12 @@
       </c>
       <c r="BB188" t="n">
         <v>1147.61</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>-13949</v>
       </c>
     </row>
     <row r="189">
@@ -29053,10 +30023,10 @@
         <v>-33.62</v>
       </c>
       <c r="AG189" t="n">
-        <v>2510</v>
+        <v>2510000000</v>
       </c>
       <c r="AH189" t="n">
-        <v>2540</v>
+        <v>2540000000</v>
       </c>
       <c r="AI189" t="n">
         <v>892</v>
@@ -29117,6 +30087,12 @@
       </c>
       <c r="BB189" t="n">
         <v>144.91</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>-228238</v>
       </c>
     </row>
     <row r="190">
@@ -29210,10 +30186,10 @@
         <v>84.94</v>
       </c>
       <c r="AG190" t="n">
-        <v>869.7</v>
+        <v>869700000</v>
       </c>
       <c r="AH190" t="n">
-        <v>851.4</v>
+        <v>851400000</v>
       </c>
       <c r="AI190" t="n">
         <v>828.9</v>
@@ -29243,7 +30219,7 @@
         <v>4.5</v>
       </c>
       <c r="AR190" t="n">
-        <v>52.66</v>
+        <v>52.65</v>
       </c>
       <c r="AS190" t="n">
         <v>150.83</v>
@@ -29274,6 +30250,12 @@
       </c>
       <c r="BB190" t="n">
         <v>229.71</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>-49188</v>
       </c>
     </row>
     <row r="191">
@@ -29346,10 +30328,10 @@
         <v>10.95</v>
       </c>
       <c r="AG191" t="n">
-        <v>1590</v>
+        <v>1590000000</v>
       </c>
       <c r="AH191" t="n">
-        <v>1710</v>
+        <v>1710000000</v>
       </c>
       <c r="AI191" t="n">
         <v>2050</v>
@@ -29407,6 +30389,12 @@
       </c>
       <c r="BB191" t="n">
         <v>202.42</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>-457440</v>
       </c>
     </row>
     <row r="192">
@@ -29500,10 +30488,10 @@
         <v>15.92</v>
       </c>
       <c r="AG192" t="n">
-        <v>76.64</v>
+        <v>76640000</v>
       </c>
       <c r="AH192" t="n">
-        <v>81.22</v>
+        <v>81220000</v>
       </c>
       <c r="AI192" t="n">
         <v>121.74</v>
@@ -29558,6 +30546,12 @@
       </c>
       <c r="BB192" t="n">
         <v>540.61</v>
+      </c>
+      <c r="BC192" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD192" t="n">
+        <v>1802</v>
       </c>
     </row>
     <row r="193">
@@ -29651,10 +30645,10 @@
         <v>18.3</v>
       </c>
       <c r="AG193" t="n">
-        <v>7450</v>
+        <v>7450000000</v>
       </c>
       <c r="AH193" t="n">
-        <v>7470</v>
+        <v>7470000000</v>
       </c>
       <c r="AI193" t="n">
         <v>12410</v>
@@ -29715,6 +30709,12 @@
       </c>
       <c r="BB193" t="n">
         <v>490.3</v>
+      </c>
+      <c r="BC193" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BD193" t="n">
+        <v>-4517</v>
       </c>
     </row>
     <row r="194">
@@ -29808,10 +30808,10 @@
         <v>14.77</v>
       </c>
       <c r="AG194" t="n">
-        <v>169</v>
+        <v>169000000</v>
       </c>
       <c r="AH194" t="n">
-        <v>171.9</v>
+        <v>171900000</v>
       </c>
       <c r="AI194" t="n">
         <v>357</v>
@@ -29872,6 +30872,12 @@
       </c>
       <c r="BB194" t="n">
         <v>460.53</v>
+      </c>
+      <c r="BC194" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD194" t="n">
+        <v>-22428</v>
       </c>
     </row>
     <row r="195">
@@ -29965,10 +30971,10 @@
         <v>-5.05</v>
       </c>
       <c r="AG195" t="n">
-        <v>55.89</v>
+        <v>55890000</v>
       </c>
       <c r="AH195" t="n">
-        <v>56.05</v>
+        <v>56050000</v>
       </c>
       <c r="AI195" t="n">
         <v>17</v>
@@ -30029,6 +31035,12 @@
       </c>
       <c r="BB195" t="n">
         <v>120.48</v>
+      </c>
+      <c r="BC195" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD195" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -30110,10 +31122,10 @@
         <v>1.9</v>
       </c>
       <c r="AG196" t="n">
-        <v>277.66</v>
+        <v>277660000</v>
       </c>
       <c r="AH196" t="n">
-        <v>113.21</v>
+        <v>113210000</v>
       </c>
       <c r="AI196" t="n">
         <v>53.25</v>
@@ -30162,6 +31174,12 @@
       </c>
       <c r="BB196" t="n">
         <v>126.18</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>-17606</v>
       </c>
     </row>
     <row r="197">
@@ -30249,10 +31267,10 @@
         <v>42.61</v>
       </c>
       <c r="AG197" t="n">
-        <v>73.98999999999999</v>
+        <v>73990000</v>
       </c>
       <c r="AH197" t="n">
-        <v>71.17</v>
+        <v>71170000</v>
       </c>
       <c r="AI197" t="n">
         <v>83.64</v>
@@ -30313,6 +31331,12 @@
       </c>
       <c r="BB197" t="n">
         <v>251.75</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>-10261</v>
       </c>
     </row>
     <row r="198">
@@ -30403,10 +31427,10 @@
         <v>142.48</v>
       </c>
       <c r="AG198" t="n">
-        <v>1130</v>
+        <v>1130000000</v>
       </c>
       <c r="AH198" t="n">
-        <v>1120</v>
+        <v>1120000000</v>
       </c>
       <c r="AI198" t="n">
         <v>1210</v>
@@ -30467,6 +31491,12 @@
       </c>
       <c r="BB198" t="n">
         <v>926.55</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>-178789</v>
       </c>
     </row>
     <row r="199">
@@ -30557,10 +31587,10 @@
         <v>65.59999999999999</v>
       </c>
       <c r="AG199" t="n">
-        <v>157.5</v>
+        <v>157500000</v>
       </c>
       <c r="AH199" t="n">
-        <v>158</v>
+        <v>158000000</v>
       </c>
       <c r="AI199" t="n">
         <v>18.3</v>
@@ -30621,6 +31651,12 @@
       </c>
       <c r="BB199" t="n">
         <v>22.74</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>-65569</v>
       </c>
     </row>
     <row r="200">
@@ -30708,10 +31744,10 @@
         <v>500.79</v>
       </c>
       <c r="AG200" t="n">
-        <v>247.68</v>
+        <v>247680000</v>
       </c>
       <c r="AH200" t="n">
-        <v>368.02</v>
+        <v>368020000</v>
       </c>
       <c r="AI200" t="n">
         <v>188.9</v>
@@ -30760,6 +31796,12 @@
       </c>
       <c r="BB200" t="n">
         <v>209.37</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>-142902</v>
       </c>
     </row>
     <row r="201">
@@ -30850,10 +31892,10 @@
         <v>71.29000000000001</v>
       </c>
       <c r="AG201" t="n">
-        <v>1110</v>
+        <v>1110000000</v>
       </c>
       <c r="AH201" t="n">
-        <v>795</v>
+        <v>795000000</v>
       </c>
       <c r="AI201" t="n">
         <v>99</v>
@@ -30914,6 +31956,12 @@
       </c>
       <c r="BB201" t="n">
         <v>121.76</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>-7347</v>
       </c>
     </row>
     <row r="202">
@@ -30998,10 +32046,10 @@
         <v>33.6</v>
       </c>
       <c r="AG202" t="n">
-        <v>348.42</v>
+        <v>348420000</v>
       </c>
       <c r="AH202" t="n">
-        <v>326.33</v>
+        <v>326330000</v>
       </c>
       <c r="AI202" t="n">
         <v>507.65</v>
@@ -31056,6 +32104,12 @@
       </c>
       <c r="BB202" t="n">
         <v>324.65</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>-916751</v>
       </c>
     </row>
     <row r="203">
@@ -31149,10 +32203,10 @@
         <v>30.09</v>
       </c>
       <c r="AG203" t="n">
-        <v>4340</v>
+        <v>4340000000</v>
       </c>
       <c r="AH203" t="n">
-        <v>4510</v>
+        <v>4510000000</v>
       </c>
       <c r="AI203" t="n">
         <v>487.33</v>
@@ -31210,6 +32264,12 @@
       </c>
       <c r="BB203" t="n">
         <v>76.41</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>-248079</v>
       </c>
     </row>
     <row r="204">
@@ -31303,10 +32363,10 @@
         <v>333.64</v>
       </c>
       <c r="AG204" t="n">
-        <v>1480</v>
+        <v>1480000000</v>
       </c>
       <c r="AH204" t="n">
-        <v>1570</v>
+        <v>1570000000</v>
       </c>
       <c r="AI204" t="n">
         <v>715</v>
@@ -31367,6 +32427,12 @@
       </c>
       <c r="BB204" t="n">
         <v>35.78</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>344718</v>
       </c>
     </row>
     <row r="205">
@@ -31460,10 +32526,10 @@
         <v>44.72</v>
       </c>
       <c r="AG205" t="n">
-        <v>1050</v>
+        <v>1050000000</v>
       </c>
       <c r="AH205" t="n">
-        <v>1020</v>
+        <v>1020000000</v>
       </c>
       <c r="AI205" t="n">
         <v>2200</v>
@@ -31521,6 +32587,12 @@
       </c>
       <c r="BB205" t="n">
         <v>139.82</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>-14546</v>
       </c>
     </row>
     <row r="206">
@@ -31611,10 +32683,10 @@
         <v>34.77</v>
       </c>
       <c r="AG206" t="n">
-        <v>201</v>
+        <v>201000000</v>
       </c>
       <c r="AH206" t="n">
-        <v>220</v>
+        <v>220000000</v>
       </c>
       <c r="AI206" t="n">
         <v>397</v>
@@ -31675,6 +32747,12 @@
       </c>
       <c r="BB206" t="n">
         <v>191.49</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>-34450</v>
       </c>
     </row>
     <row r="207">
@@ -31732,10 +32810,10 @@
         <v>43.88</v>
       </c>
       <c r="AG207" t="n">
-        <v>4910</v>
+        <v>4910000000</v>
       </c>
       <c r="AH207" t="n">
-        <v>4680</v>
+        <v>4680000000</v>
       </c>
       <c r="AI207" t="n">
         <v>331.58</v>
@@ -31787,6 +32865,12 @@
       </c>
       <c r="BB207" t="n">
         <v>13.81</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>1974855</v>
       </c>
     </row>
     <row r="208">
@@ -31880,10 +32964,10 @@
         <v>36.45</v>
       </c>
       <c r="AG208" t="n">
-        <v>231</v>
+        <v>231000000</v>
       </c>
       <c r="AH208" t="n">
-        <v>263.2</v>
+        <v>263200000</v>
       </c>
       <c r="AI208" t="n">
         <v>146</v>
@@ -31944,6 +33028,12 @@
       </c>
       <c r="BB208" t="n">
         <v>260.68</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>-45916</v>
       </c>
     </row>
     <row r="209">
@@ -32034,10 +33124,10 @@
         <v>84.31999999999999</v>
       </c>
       <c r="AG209" t="n">
-        <v>24510</v>
+        <v>24510000000</v>
       </c>
       <c r="AH209" t="n">
-        <v>25070</v>
+        <v>25070000000</v>
       </c>
       <c r="AI209" t="n">
         <v>7240</v>
@@ -32098,6 +33188,12 @@
       </c>
       <c r="BB209" t="n">
         <v>213.9</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>-5294074</v>
       </c>
     </row>
     <row r="210">
@@ -32188,10 +33284,10 @@
         <v>9.23</v>
       </c>
       <c r="AG210" t="n">
-        <v>32.8</v>
+        <v>32800000</v>
       </c>
       <c r="AH210" t="n">
-        <v>31.87</v>
+        <v>31870000</v>
       </c>
       <c r="AI210" t="n">
         <v>27.73</v>
@@ -32252,6 +33348,12 @@
       </c>
       <c r="BB210" t="n">
         <v>339.25</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>4563</v>
       </c>
     </row>
     <row r="211">
@@ -32345,10 +33447,10 @@
         <v>51.49</v>
       </c>
       <c r="AG211" t="n">
-        <v>164.6</v>
+        <v>164600000</v>
       </c>
       <c r="AH211" t="n">
-        <v>168.3</v>
+        <v>168300000</v>
       </c>
       <c r="AI211" t="n">
         <v>40.5</v>
@@ -32409,6 +33511,12 @@
       </c>
       <c r="BB211" t="n">
         <v>147.65</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>-75808</v>
       </c>
     </row>
     <row r="212">
@@ -32487,10 +33595,10 @@
         <v>-59.42</v>
       </c>
       <c r="AG212" t="n">
-        <v>205.57</v>
+        <v>205570000</v>
       </c>
       <c r="AH212" t="n">
-        <v>145.74</v>
+        <v>145740000</v>
       </c>
       <c r="AI212" t="n">
         <v>41.75</v>
@@ -32533,6 +33641,12 @@
       </c>
       <c r="BB212" t="n">
         <v>10.48</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>81735</v>
       </c>
     </row>
     <row r="213">
@@ -32626,10 +33740,10 @@
         <v>13.75</v>
       </c>
       <c r="AG213" t="n">
-        <v>254.33</v>
+        <v>254330000</v>
       </c>
       <c r="AH213" t="n">
-        <v>264.05</v>
+        <v>264050000</v>
       </c>
       <c r="AI213" t="n">
         <v>432</v>
@@ -32659,7 +33773,7 @@
         <v>6.4</v>
       </c>
       <c r="AR213" t="n">
-        <v>40.52</v>
+        <v>40.53</v>
       </c>
       <c r="AS213" t="n">
         <v>14.12</v>
@@ -32690,6 +33804,12 @@
       </c>
       <c r="BB213" t="n">
         <v>218.98</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -32780,10 +33900,10 @@
         <v>-18.42</v>
       </c>
       <c r="AG214" t="n">
-        <v>152.71</v>
+        <v>152710000</v>
       </c>
       <c r="AH214" t="n">
-        <v>145.85</v>
+        <v>145850000</v>
       </c>
       <c r="AI214" t="n">
         <v>127.63</v>
@@ -32838,6 +33958,12 @@
       </c>
       <c r="BB214" t="n">
         <v>78.03</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>-73084</v>
       </c>
     </row>
     <row r="215">
@@ -32928,10 +34054,10 @@
         <v>-8.91</v>
       </c>
       <c r="AG215" t="n">
-        <v>211.6</v>
+        <v>211600000</v>
       </c>
       <c r="AH215" t="n">
-        <v>226.16</v>
+        <v>226160000</v>
       </c>
       <c r="AI215" t="n">
         <v>12.85</v>
@@ -32989,6 +34115,12 @@
       </c>
       <c r="BB215" t="n">
         <v>174.36</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>-19952</v>
       </c>
     </row>
     <row r="216">
@@ -33082,10 +34214,10 @@
         <v>-34.22</v>
       </c>
       <c r="AG216" t="n">
-        <v>411.8</v>
+        <v>411800000</v>
       </c>
       <c r="AH216" t="n">
-        <v>448.2</v>
+        <v>448200000</v>
       </c>
       <c r="AI216" t="n">
         <v>150.7</v>
@@ -33130,7 +34262,7 @@
         <v>85</v>
       </c>
       <c r="AW216" t="n">
-        <v>106.88</v>
+        <v>106.28</v>
       </c>
       <c r="AX216" t="n">
         <v>10.17</v>
@@ -33146,6 +34278,12 @@
       </c>
       <c r="BB216" t="n">
         <v>66.59999999999999</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>116</v>
       </c>
     </row>
     <row r="217">
@@ -33236,10 +34374,10 @@
         <v>79.12</v>
       </c>
       <c r="AG217" t="n">
-        <v>333.86</v>
+        <v>333860000</v>
       </c>
       <c r="AH217" t="n">
-        <v>319.78</v>
+        <v>319780000</v>
       </c>
       <c r="AI217" t="n">
         <v>92.33</v>
@@ -33294,6 +34432,12 @@
       </c>
       <c r="BB217" t="n">
         <v>27.15</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>139582</v>
       </c>
     </row>
     <row r="218">
@@ -33384,10 +34528,10 @@
         <v>-7.08</v>
       </c>
       <c r="AG218" t="n">
-        <v>49.27</v>
+        <v>49270000</v>
       </c>
       <c r="AH218" t="n">
-        <v>49.76</v>
+        <v>49760000</v>
       </c>
       <c r="AI218" t="n">
         <v>31.15</v>
@@ -33448,6 +34592,12 @@
       </c>
       <c r="BB218" t="n">
         <v>243.64</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>-8994</v>
       </c>
     </row>
     <row r="219">
@@ -33541,10 +34691,10 @@
         <v>33.84</v>
       </c>
       <c r="AG219" t="n">
-        <v>2910</v>
+        <v>2910000000</v>
       </c>
       <c r="AH219" t="n">
-        <v>2770</v>
+        <v>2770000000</v>
       </c>
       <c r="AI219" t="n">
         <v>4810</v>
@@ -33602,6 +34752,12 @@
       </c>
       <c r="BB219" t="n">
         <v>143.16</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>-400000</v>
       </c>
     </row>
     <row r="220">
@@ -33686,10 +34842,10 @@
         <v>17.25</v>
       </c>
       <c r="AG220" t="n">
-        <v>262.39</v>
+        <v>262390000</v>
       </c>
       <c r="AH220" t="n">
-        <v>212.47</v>
+        <v>212470000</v>
       </c>
       <c r="AI220" t="n">
         <v>75.19</v>
@@ -33741,6 +34897,12 @@
       </c>
       <c r="BB220" t="n">
         <v>32.34</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>-4369757</v>
       </c>
     </row>
     <row r="221">
@@ -33831,10 +34993,10 @@
         <v>-46.36</v>
       </c>
       <c r="AG221" t="n">
-        <v>764</v>
+        <v>764000000</v>
       </c>
       <c r="AH221" t="n">
-        <v>684.5</v>
+        <v>684500000</v>
       </c>
       <c r="AI221" t="n">
         <v>1810</v>
@@ -33892,6 +35054,12 @@
       </c>
       <c r="BB221" t="n">
         <v>375.65</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>-15249</v>
       </c>
     </row>
     <row r="222">
@@ -33985,10 +35153,10 @@
         <v>19.68</v>
       </c>
       <c r="AG222" t="n">
-        <v>128.1</v>
+        <v>128100000</v>
       </c>
       <c r="AH222" t="n">
-        <v>129.9</v>
+        <v>129900000</v>
       </c>
       <c r="AI222" t="n">
         <v>179</v>
@@ -34049,6 +35217,12 @@
       </c>
       <c r="BB222" t="n">
         <v>918.75</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>-20592</v>
       </c>
     </row>
     <row r="223">
@@ -34139,10 +35313,10 @@
         <v>5110.49</v>
       </c>
       <c r="AG223" t="n">
-        <v>2570</v>
+        <v>2570000000</v>
       </c>
       <c r="AH223" t="n">
-        <v>2060</v>
+        <v>2060000000</v>
       </c>
       <c r="AI223" t="n">
         <v>835.52</v>
@@ -34200,6 +35374,12 @@
       </c>
       <c r="BB223" t="n">
         <v>174.34</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>-1102027</v>
       </c>
     </row>
     <row r="224">
@@ -34290,10 +35470,10 @@
         <v>-1.57</v>
       </c>
       <c r="AG224" t="n">
-        <v>27.62</v>
+        <v>27620000</v>
       </c>
       <c r="AH224" t="n">
-        <v>28.44</v>
+        <v>28440000</v>
       </c>
       <c r="AI224" t="n">
         <v>44.62</v>
@@ -34354,6 +35534,12 @@
       </c>
       <c r="BB224" t="n">
         <v>242.33</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>-9000</v>
       </c>
     </row>
     <row r="225">
@@ -34447,10 +35633,10 @@
         <v>52.71</v>
       </c>
       <c r="AG225" t="n">
-        <v>71.89</v>
+        <v>71890000</v>
       </c>
       <c r="AH225" t="n">
-        <v>69.91</v>
+        <v>69910000</v>
       </c>
       <c r="AI225" t="n">
         <v>77.90000000000001</v>
@@ -34511,6 +35697,12 @@
       </c>
       <c r="BB225" t="n">
         <v>140.6</v>
+      </c>
+      <c r="BC225" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD225" t="n">
+        <v>2362</v>
       </c>
     </row>
     <row r="226">
@@ -34604,10 +35796,10 @@
         <v>132.5</v>
       </c>
       <c r="AG226" t="n">
-        <v>120.78</v>
+        <v>120780000</v>
       </c>
       <c r="AH226" t="n">
-        <v>118.23</v>
+        <v>118230000</v>
       </c>
       <c r="AI226" t="n">
         <v>240.66</v>
@@ -34665,6 +35857,12 @@
       </c>
       <c r="BB226" t="n">
         <v>131.16</v>
+      </c>
+      <c r="BC226" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD226" t="n">
+        <v>2068</v>
       </c>
     </row>
     <row r="227">
@@ -34758,10 +35956,10 @@
         <v>-7.12</v>
       </c>
       <c r="AG227" t="n">
-        <v>151.29</v>
+        <v>151290000</v>
       </c>
       <c r="AH227" t="n">
-        <v>147.99</v>
+        <v>147990000</v>
       </c>
       <c r="AI227" t="n">
         <v>225.74</v>
@@ -34822,6 +36020,12 @@
       </c>
       <c r="BB227" t="n">
         <v>619.28</v>
+      </c>
+      <c r="BC227" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD227" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -34915,10 +36119,10 @@
         <v>4.33</v>
       </c>
       <c r="AG228" t="n">
-        <v>968</v>
+        <v>968000000</v>
       </c>
       <c r="AH228" t="n">
-        <v>1160</v>
+        <v>1160000000</v>
       </c>
       <c r="AI228" t="n">
         <v>1100</v>
@@ -34976,6 +36180,12 @@
       </c>
       <c r="BB228" t="n">
         <v>52.71</v>
+      </c>
+      <c r="BC228" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD228" t="n">
+        <v>-14175</v>
       </c>
     </row>
     <row r="229">
@@ -35069,10 +36279,10 @@
         <v>10.76</v>
       </c>
       <c r="AG229" t="n">
-        <v>1100</v>
+        <v>1100000000</v>
       </c>
       <c r="AH229" t="n">
-        <v>1140</v>
+        <v>1140000000</v>
       </c>
       <c r="AI229" t="n">
         <v>3240</v>
@@ -35133,6 +36343,12 @@
       </c>
       <c r="BB229" t="n">
         <v>184.84</v>
+      </c>
+      <c r="BC229" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD229" t="n">
+        <v>-11192</v>
       </c>
     </row>
     <row r="230">
@@ -35226,10 +36442,10 @@
         <v>10.78</v>
       </c>
       <c r="AG230" t="n">
-        <v>178.32</v>
+        <v>178320000</v>
       </c>
       <c r="AH230" t="n">
-        <v>183.12</v>
+        <v>183120000</v>
       </c>
       <c r="AI230" t="n">
         <v>30.22</v>
@@ -35281,6 +36497,9 @@
       </c>
       <c r="BB230" t="n">
         <v>412.34</v>
+      </c>
+      <c r="BD230" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -35374,10 +36593,10 @@
         <v>47.87</v>
       </c>
       <c r="AG231" t="n">
-        <v>274</v>
+        <v>274000000</v>
       </c>
       <c r="AH231" t="n">
-        <v>255</v>
+        <v>255000000</v>
       </c>
       <c r="AI231" t="n">
         <v>151</v>
@@ -35438,6 +36657,12 @@
       </c>
       <c r="BB231" t="n">
         <v>253.92</v>
+      </c>
+      <c r="BC231" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD231" t="n">
+        <v>-12128</v>
       </c>
     </row>
     <row r="232">
@@ -35531,10 +36756,10 @@
         <v>15.34</v>
       </c>
       <c r="AG232" t="n">
-        <v>1640</v>
+        <v>1640000000</v>
       </c>
       <c r="AH232" t="n">
-        <v>1630</v>
+        <v>1630000000</v>
       </c>
       <c r="AI232" t="n">
         <v>237</v>
@@ -35583,6 +36808,9 @@
       </c>
       <c r="BB232" t="n">
         <v>95.79000000000001</v>
+      </c>
+      <c r="BD232" t="n">
+        <v>-2961034</v>
       </c>
     </row>
     <row r="233">
@@ -35667,10 +36895,10 @@
         <v>35.7</v>
       </c>
       <c r="AG233" t="n">
-        <v>530.66</v>
+        <v>530660000</v>
       </c>
       <c r="AH233" t="n">
-        <v>466.21</v>
+        <v>466210000</v>
       </c>
       <c r="AI233" t="n">
         <v>81.61</v>
@@ -35719,6 +36947,12 @@
       </c>
       <c r="BB233" t="n">
         <v>63.7</v>
+      </c>
+      <c r="BC233" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD233" t="n">
+        <v>-3654371</v>
       </c>
     </row>
     <row r="234">
@@ -35812,10 +37046,10 @@
         <v>79.51000000000001</v>
       </c>
       <c r="AG234" t="n">
-        <v>62.3</v>
+        <v>62300000</v>
       </c>
       <c r="AH234" t="n">
-        <v>69</v>
+        <v>69000000</v>
       </c>
       <c r="AI234" t="n">
         <v>114.6</v>
@@ -35876,6 +37110,12 @@
       </c>
       <c r="BB234" t="n">
         <v>338.36</v>
+      </c>
+      <c r="BC234" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD234" t="n">
+        <v>396</v>
       </c>
     </row>
     <row r="235">
@@ -35966,10 +37206,10 @@
         <v>22.41</v>
       </c>
       <c r="AG235" t="n">
-        <v>109.23</v>
+        <v>109230000</v>
       </c>
       <c r="AH235" t="n">
-        <v>109.47</v>
+        <v>109470000</v>
       </c>
       <c r="AI235" t="n">
         <v>55.99</v>
@@ -36030,6 +37270,12 @@
       </c>
       <c r="BB235" t="n">
         <v>81.41</v>
+      </c>
+      <c r="BC235" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD235" t="n">
+        <v>-5000</v>
       </c>
     </row>
     <row r="236">
@@ -36120,10 +37366,10 @@
         <v>-1.08</v>
       </c>
       <c r="AG236" t="n">
-        <v>146.05</v>
+        <v>146050000</v>
       </c>
       <c r="AH236" t="n">
-        <v>147.46</v>
+        <v>147460000</v>
       </c>
       <c r="AI236" t="n">
         <v>104.35</v>
@@ -36184,6 +37430,12 @@
       </c>
       <c r="BB236" t="n">
         <v>228.25</v>
+      </c>
+      <c r="BC236" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BD236" t="n">
+        <v>-23943</v>
       </c>
     </row>
     <row r="237">
@@ -36274,10 +37526,10 @@
         <v>7.46</v>
       </c>
       <c r="AG237" t="n">
-        <v>105.04</v>
+        <v>105040000</v>
       </c>
       <c r="AH237" t="n">
-        <v>104.94</v>
+        <v>104940000</v>
       </c>
       <c r="AI237" t="n">
         <v>202.12</v>
@@ -36431,10 +37683,10 @@
         <v>43.71</v>
       </c>
       <c r="AG238" t="n">
-        <v>113.1</v>
+        <v>113100000</v>
       </c>
       <c r="AH238" t="n">
-        <v>116.7</v>
+        <v>116700000</v>
       </c>
       <c r="AI238" t="n">
         <v>89</v>
@@ -36495,6 +37747,12 @@
       </c>
       <c r="BB238" t="n">
         <v>414.92</v>
+      </c>
+      <c r="BC238" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD238" t="n">
+        <v>-1586</v>
       </c>
     </row>
     <row r="239">
@@ -36582,10 +37840,10 @@
         <v>16.14</v>
       </c>
       <c r="AG239" t="n">
-        <v>150.91</v>
+        <v>150910000</v>
       </c>
       <c r="AH239" t="n">
-        <v>137.67</v>
+        <v>137670000</v>
       </c>
       <c r="AI239" t="n">
         <v>328.04</v>
@@ -36646,6 +37904,12 @@
       </c>
       <c r="BB239" t="n">
         <v>155.12</v>
+      </c>
+      <c r="BC239" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD239" t="n">
+        <v>-118636</v>
       </c>
     </row>
     <row r="240">
@@ -36739,10 +38003,10 @@
         <v>12.12</v>
       </c>
       <c r="AG240" t="n">
-        <v>108.2</v>
+        <v>108200000</v>
       </c>
       <c r="AH240" t="n">
-        <v>106.8</v>
+        <v>106800000</v>
       </c>
       <c r="AI240" t="n">
         <v>191.8</v>
@@ -36803,6 +38067,12 @@
       </c>
       <c r="BB240" t="n">
         <v>375.82</v>
+      </c>
+      <c r="BC240" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD240" t="n">
+        <v>-8434</v>
       </c>
     </row>
     <row r="241">
@@ -36896,10 +38166,10 @@
         <v>11.37</v>
       </c>
       <c r="AG241" t="n">
-        <v>324.42</v>
+        <v>324420000</v>
       </c>
       <c r="AH241" t="n">
-        <v>345.22</v>
+        <v>345220000</v>
       </c>
       <c r="AI241" t="n">
         <v>198.49</v>
@@ -36960,6 +38230,12 @@
       </c>
       <c r="BB241" t="n">
         <v>224.8</v>
+      </c>
+      <c r="BC241" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD241" t="n">
+        <v>-104562</v>
       </c>
     </row>
     <row r="242">
@@ -37053,10 +38329,10 @@
         <v>17.73</v>
       </c>
       <c r="AG242" t="n">
-        <v>55.18</v>
+        <v>55180000</v>
       </c>
       <c r="AH242" t="n">
-        <v>63.12</v>
+        <v>63120000</v>
       </c>
       <c r="AI242" t="n">
         <v>88.73999999999999</v>
@@ -37117,6 +38393,12 @@
       </c>
       <c r="BB242" t="n">
         <v>195.75</v>
+      </c>
+      <c r="BC242" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD242" t="n">
+        <v>-120</v>
       </c>
     </row>
     <row r="243">
@@ -37210,10 +38492,10 @@
         <v>-14.39</v>
       </c>
       <c r="AG243" t="n">
-        <v>1140</v>
+        <v>1140000000</v>
       </c>
       <c r="AH243" t="n">
-        <v>1160</v>
+        <v>1160000000</v>
       </c>
       <c r="AI243" t="n">
         <v>364.4</v>
@@ -37271,6 +38553,12 @@
       </c>
       <c r="BB243" t="n">
         <v>97.34</v>
+      </c>
+      <c r="BC243" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD243" t="n">
+        <v>-62954</v>
       </c>
     </row>
     <row r="244">
@@ -37361,10 +38649,10 @@
         <v>84.87</v>
       </c>
       <c r="AG244" t="n">
-        <v>638.23</v>
+        <v>638230000</v>
       </c>
       <c r="AH244" t="n">
-        <v>558.12</v>
+        <v>558120000</v>
       </c>
       <c r="AI244" t="n">
         <v>625</v>
@@ -37422,6 +38710,12 @@
       </c>
       <c r="BB244" t="n">
         <v>103.5</v>
+      </c>
+      <c r="BC244" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD244" t="n">
+        <v>-17395</v>
       </c>
     </row>
     <row r="245">
@@ -37515,10 +38809,10 @@
         <v>42.84</v>
       </c>
       <c r="AG245" t="n">
-        <v>35.74</v>
+        <v>35740000</v>
       </c>
       <c r="AH245" t="n">
-        <v>32.66</v>
+        <v>32660000</v>
       </c>
       <c r="AI245" t="n">
         <v>7.18</v>
@@ -37570,6 +38864,12 @@
       </c>
       <c r="BB245" t="n">
         <v>117.32</v>
+      </c>
+      <c r="BC245" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="BD245" t="n">
+        <v>-1620539</v>
       </c>
     </row>
     <row r="246">
@@ -37660,10 +38960,10 @@
         <v>37.71</v>
       </c>
       <c r="AG246" t="n">
-        <v>1300</v>
+        <v>1300000000</v>
       </c>
       <c r="AH246" t="n">
-        <v>1270</v>
+        <v>1270000000</v>
       </c>
       <c r="AI246" t="n">
         <v>482</v>
@@ -37721,6 +39021,12 @@
       </c>
       <c r="BB246" t="n">
         <v>129.96</v>
+      </c>
+      <c r="BC246" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD246" t="n">
+        <v>-620237</v>
       </c>
     </row>
     <row r="247">
@@ -37811,10 +39117,10 @@
         <v>79.29000000000001</v>
       </c>
       <c r="AG247" t="n">
-        <v>33.68</v>
+        <v>33680000</v>
       </c>
       <c r="AH247" t="n">
-        <v>33.39</v>
+        <v>33390000</v>
       </c>
       <c r="AI247" t="n">
         <v>33.09</v>
@@ -37875,6 +39181,12 @@
       </c>
       <c r="BB247" t="n">
         <v>241.14</v>
+      </c>
+      <c r="BC247" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD247" t="n">
+        <v>-5000</v>
       </c>
     </row>
     <row r="248">
@@ -37965,10 +39277,10 @@
         <v>-7.28</v>
       </c>
       <c r="AG248" t="n">
-        <v>88.37</v>
+        <v>88370000</v>
       </c>
       <c r="AH248" t="n">
-        <v>64.01000000000001</v>
+        <v>64010000</v>
       </c>
       <c r="AI248" t="n">
         <v>83.88</v>
@@ -38029,6 +39341,12 @@
       </c>
       <c r="BB248" t="n">
         <v>167.55</v>
+      </c>
+      <c r="BC248" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BD248" t="n">
+        <v>-47471</v>
       </c>
     </row>
     <row r="249">
@@ -38119,10 +39437,10 @@
         <v>75.62</v>
       </c>
       <c r="AG249" t="n">
-        <v>142.09</v>
+        <v>142090000</v>
       </c>
       <c r="AH249" t="n">
-        <v>138.98</v>
+        <v>138980000</v>
       </c>
       <c r="AI249" t="n">
         <v>98.92</v>
@@ -38177,6 +39495,12 @@
       </c>
       <c r="BB249" t="n">
         <v>170.68</v>
+      </c>
+      <c r="BC249" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD249" t="n">
+        <v>-3688347</v>
       </c>
     </row>
     <row r="250">
@@ -38264,7 +39588,7 @@
         <v>13694.12</v>
       </c>
       <c r="AG250" t="n">
-        <v>155</v>
+        <v>155000000</v>
       </c>
       <c r="AI250" t="n">
         <v>232</v>
@@ -38319,6 +39643,12 @@
       </c>
       <c r="BB250" t="n">
         <v>1519.97</v>
+      </c>
+      <c r="BC250" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD250" t="n">
+        <v>-113716</v>
       </c>
     </row>
     <row r="251">
@@ -38403,10 +39733,10 @@
         <v>30.12</v>
       </c>
       <c r="AG251" t="n">
-        <v>337.49</v>
+        <v>337490000</v>
       </c>
       <c r="AH251" t="n">
-        <v>318.73</v>
+        <v>318730000</v>
       </c>
       <c r="AI251" t="n">
         <v>1640</v>
@@ -38461,6 +39791,12 @@
       </c>
       <c r="BB251" t="n">
         <v>331.02</v>
+      </c>
+      <c r="BC251" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD251" t="n">
+        <v>-1742689</v>
       </c>
     </row>
     <row r="252">
@@ -38530,10 +39866,10 @@
         <v>40.21</v>
       </c>
       <c r="AG252" t="n">
-        <v>1250</v>
+        <v>1250000000</v>
       </c>
       <c r="AH252" t="n">
-        <v>900.89</v>
+        <v>900890000</v>
       </c>
       <c r="AI252" t="n">
         <v>283.92</v>
@@ -38588,6 +39924,12 @@
       </c>
       <c r="BB252" t="n">
         <v>16.84</v>
+      </c>
+      <c r="BC252" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="BD252" t="n">
+        <v>-284208</v>
       </c>
     </row>
     <row r="253">
@@ -38636,7 +39978,7 @@
         <v>-3440</v>
       </c>
       <c r="AG253" t="n">
-        <v>2930</v>
+        <v>2930000000</v>
       </c>
       <c r="AI253" t="n">
         <v>2720</v>
@@ -38679,6 +40021,12 @@
       </c>
       <c r="BB253" t="n">
         <v>150.88</v>
+      </c>
+      <c r="BC253" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BD253" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -38769,10 +40117,10 @@
         <v>52.88</v>
       </c>
       <c r="AG254" t="n">
-        <v>210.51</v>
+        <v>210510000</v>
       </c>
       <c r="AH254" t="n">
-        <v>195.85</v>
+        <v>195850000</v>
       </c>
       <c r="AI254" t="n">
         <v>312.89</v>
@@ -38827,6 +40175,12 @@
       </c>
       <c r="BB254" t="n">
         <v>547.4299999999999</v>
+      </c>
+      <c r="BC254" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD254" t="n">
+        <v>-61733</v>
       </c>
     </row>
     <row r="255">
@@ -38917,10 +40271,10 @@
         <v>-40.89</v>
       </c>
       <c r="AG255" t="n">
-        <v>923.05</v>
+        <v>923050000</v>
       </c>
       <c r="AH255" t="n">
-        <v>946.22</v>
+        <v>946220000</v>
       </c>
       <c r="AI255" t="n">
         <v>180</v>
@@ -38972,6 +40326,9 @@
       </c>
       <c r="BB255" t="n">
         <v>48.06</v>
+      </c>
+      <c r="BD255" t="n">
+        <v>164049</v>
       </c>
     </row>
     <row r="256">
@@ -39062,10 +40419,10 @@
         <v>84.87</v>
       </c>
       <c r="AG256" t="n">
-        <v>30.95</v>
+        <v>30950000</v>
       </c>
       <c r="AH256" t="n">
-        <v>30.56</v>
+        <v>30560000</v>
       </c>
       <c r="AI256" t="n">
         <v>27.54</v>
@@ -39123,6 +40480,12 @@
       </c>
       <c r="BB256" t="n">
         <v>482.67</v>
+      </c>
+      <c r="BC256" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD256" t="n">
+        <v>-9940</v>
       </c>
     </row>
     <row r="257">
@@ -39216,10 +40579,10 @@
         <v>167.64</v>
       </c>
       <c r="AG257" t="n">
-        <v>229</v>
+        <v>229000000</v>
       </c>
       <c r="AH257" t="n">
-        <v>207</v>
+        <v>207000000</v>
       </c>
       <c r="AI257" t="n">
         <v>213</v>
@@ -39280,6 +40643,12 @@
       </c>
       <c r="BB257" t="n">
         <v>783.1799999999999</v>
+      </c>
+      <c r="BC257" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD257" t="n">
+        <v>-173716</v>
       </c>
     </row>
     <row r="258">
@@ -39373,10 +40742,10 @@
         <v>-24.74</v>
       </c>
       <c r="AG258" t="n">
-        <v>175.57</v>
+        <v>175570000</v>
       </c>
       <c r="AH258" t="n">
-        <v>192.54</v>
+        <v>192540000</v>
       </c>
       <c r="AI258" t="n">
         <v>73.8</v>
@@ -39437,6 +40806,12 @@
       </c>
       <c r="BB258" t="n">
         <v>123.03</v>
+      </c>
+      <c r="BC258" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD258" t="n">
+        <v>11789</v>
       </c>
     </row>
     <row r="259">
@@ -39530,10 +40905,10 @@
         <v>3.88</v>
       </c>
       <c r="AG259" t="n">
-        <v>570.52</v>
+        <v>570520000</v>
       </c>
       <c r="AH259" t="n">
-        <v>565.16</v>
+        <v>565160000</v>
       </c>
       <c r="AI259" t="n">
         <v>278.63</v>
@@ -39594,6 +40969,9 @@
       </c>
       <c r="BB259" t="n">
         <v>279.4</v>
+      </c>
+      <c r="BD259" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -39684,10 +41062,10 @@
         <v>9.16</v>
       </c>
       <c r="AG260" t="n">
-        <v>874.79</v>
+        <v>874790000</v>
       </c>
       <c r="AH260" t="n">
-        <v>836.5599999999999</v>
+        <v>836560000</v>
       </c>
       <c r="AJ260" t="n">
         <v>-1.22</v>
@@ -39799,10 +41177,10 @@
         <v>-1.14</v>
       </c>
       <c r="AG261" t="n">
-        <v>1730</v>
+        <v>1730000000</v>
       </c>
       <c r="AH261" t="n">
-        <v>1810</v>
+        <v>1810000000</v>
       </c>
       <c r="AI261" t="n">
         <v>833.3</v>
@@ -39851,6 +41229,9 @@
       </c>
       <c r="BB261" t="n">
         <v>120.6</v>
+      </c>
+      <c r="BD261" t="n">
+        <v>-5875</v>
       </c>
     </row>
     <row r="262">
@@ -39944,10 +41325,10 @@
         <v>16.44</v>
       </c>
       <c r="AG262" t="n">
-        <v>47.4</v>
+        <v>47400000</v>
       </c>
       <c r="AH262" t="n">
-        <v>47.7</v>
+        <v>47700000</v>
       </c>
       <c r="AI262" t="n">
         <v>39.9</v>
@@ -40008,6 +41389,12 @@
       </c>
       <c r="BB262" t="n">
         <v>601.1</v>
+      </c>
+      <c r="BC262" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD262" t="n">
+        <v>-6917</v>
       </c>
     </row>
     <row r="263">
@@ -40101,10 +41488,10 @@
         <v>27.41</v>
       </c>
       <c r="AG263" t="n">
-        <v>299</v>
+        <v>299000000</v>
       </c>
       <c r="AH263" t="n">
-        <v>325</v>
+        <v>325000000</v>
       </c>
       <c r="AI263" t="n">
         <v>174</v>
@@ -40165,6 +41552,12 @@
       </c>
       <c r="BB263" t="n">
         <v>202.2</v>
+      </c>
+      <c r="BC263" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD263" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -40255,10 +41648,10 @@
         <v>105.03</v>
       </c>
       <c r="AG264" t="n">
-        <v>159.72</v>
+        <v>159720000</v>
       </c>
       <c r="AH264" t="n">
-        <v>169.73</v>
+        <v>169730000</v>
       </c>
       <c r="AI264" t="n">
         <v>73.93000000000001</v>
@@ -40319,6 +41712,12 @@
       </c>
       <c r="BB264" t="n">
         <v>341.15</v>
+      </c>
+      <c r="BC264" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD264" t="n">
+        <v>-10669</v>
       </c>
     </row>
     <row r="265">
@@ -40412,10 +41811,10 @@
         <v>27.45</v>
       </c>
       <c r="AG265" t="n">
-        <v>1130</v>
+        <v>1130000000</v>
       </c>
       <c r="AH265" t="n">
-        <v>1180</v>
+        <v>1180000000</v>
       </c>
       <c r="AI265" t="n">
         <v>223</v>
@@ -40476,6 +41875,12 @@
       </c>
       <c r="BB265" t="n">
         <v>122.84</v>
+      </c>
+      <c r="BC265" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD265" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -40563,10 +41968,10 @@
         <v>57.99</v>
       </c>
       <c r="AG266" t="n">
-        <v>45.69</v>
+        <v>45690000</v>
       </c>
       <c r="AH266" t="n">
-        <v>0.45</v>
+        <v>450000</v>
       </c>
       <c r="AI266" t="n">
         <v>568</v>
@@ -40621,6 +42026,12 @@
       </c>
       <c r="BB266" t="n">
         <v>287.6</v>
+      </c>
+      <c r="BC266" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD266" t="n">
+        <v>1770</v>
       </c>
     </row>
     <row r="267">
@@ -40711,10 +42122,10 @@
         <v>146.1</v>
       </c>
       <c r="AG267" t="n">
-        <v>40.54</v>
+        <v>40540000</v>
       </c>
       <c r="AH267" t="n">
-        <v>29.56</v>
+        <v>29560000</v>
       </c>
       <c r="AI267" t="n">
         <v>37.09</v>
@@ -40772,6 +42183,12 @@
       </c>
       <c r="BB267" t="n">
         <v>87.56</v>
+      </c>
+      <c r="BC267" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="BD267" t="n">
+        <v>61978</v>
       </c>
     </row>
     <row r="268">
@@ -40856,10 +42273,10 @@
         <v>41.19</v>
       </c>
       <c r="AG268" t="n">
-        <v>53.41</v>
+        <v>53410000</v>
       </c>
       <c r="AH268" t="n">
-        <v>51.32</v>
+        <v>51320000</v>
       </c>
       <c r="AI268" t="n">
         <v>145.96</v>
@@ -40914,6 +42331,12 @@
       </c>
       <c r="BB268" t="n">
         <v>85.84999999999999</v>
+      </c>
+      <c r="BC268" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD268" t="n">
+        <v>-2522434</v>
       </c>
     </row>
     <row r="269">
@@ -41007,10 +42430,10 @@
         <v>25.13</v>
       </c>
       <c r="AG269" t="n">
-        <v>210.2</v>
+        <v>210200000</v>
       </c>
       <c r="AH269" t="n">
-        <v>241.3</v>
+        <v>241300000</v>
       </c>
       <c r="AI269" t="n">
         <v>107.4</v>
@@ -41071,6 +42494,12 @@
       </c>
       <c r="BB269" t="n">
         <v>117.94</v>
+      </c>
+      <c r="BC269" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD269" t="n">
+        <v>106801</v>
       </c>
     </row>
     <row r="270">
@@ -41161,10 +42590,10 @@
         <v>-26.03</v>
       </c>
       <c r="AG270" t="n">
-        <v>3530</v>
+        <v>3530000000</v>
       </c>
       <c r="AH270" t="n">
-        <v>3480</v>
+        <v>3480000000</v>
       </c>
       <c r="AI270" t="n">
         <v>3800</v>
@@ -41222,6 +42651,12 @@
       </c>
       <c r="BB270" t="n">
         <v>358.08</v>
+      </c>
+      <c r="BC270" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD270" t="n">
+        <v>1328</v>
       </c>
     </row>
     <row r="271">
@@ -41312,10 +42747,10 @@
         <v>32.49</v>
       </c>
       <c r="AG271" t="n">
-        <v>25930</v>
+        <v>25930000000</v>
       </c>
       <c r="AH271" t="n">
-        <v>25930</v>
+        <v>25930000000</v>
       </c>
       <c r="AI271" t="n">
         <v>39.61</v>
@@ -41333,13 +42768,13 @@
         <v>85.72</v>
       </c>
       <c r="AN271" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="AO271" t="n">
         <v>18.3</v>
       </c>
       <c r="AP271" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ271" t="n">
         <v>6.4</v>
@@ -41364,6 +42799,9 @@
       </c>
       <c r="BB271" t="n">
         <v>417.72</v>
+      </c>
+      <c r="BD271" t="n">
+        <v>15836</v>
       </c>
     </row>
     <row r="272">
@@ -41457,10 +42895,10 @@
         <v>1.08</v>
       </c>
       <c r="AG272" t="n">
-        <v>224.9</v>
+        <v>224900000</v>
       </c>
       <c r="AH272" t="n">
-        <v>234.9</v>
+        <v>234900000</v>
       </c>
       <c r="AI272" t="n">
         <v>92</v>
@@ -41521,6 +42959,12 @@
       </c>
       <c r="BB272" t="n">
         <v>421.68</v>
+      </c>
+      <c r="BC272" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BD272" t="n">
+        <v>-43097</v>
       </c>
     </row>
     <row r="273">
@@ -41614,10 +43058,10 @@
         <v>74.26000000000001</v>
       </c>
       <c r="AG273" t="n">
-        <v>105.45</v>
+        <v>105450000</v>
       </c>
       <c r="AH273" t="n">
-        <v>103.87</v>
+        <v>103870000</v>
       </c>
       <c r="AI273" t="n">
         <v>61.34</v>
@@ -41678,6 +43122,12 @@
       </c>
       <c r="BB273" t="n">
         <v>114</v>
+      </c>
+      <c r="BC273" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD273" t="n">
+        <v>-46960</v>
       </c>
     </row>
     <row r="274">
@@ -41768,10 +43218,10 @@
         <v>174.62</v>
       </c>
       <c r="AG274" t="n">
-        <v>159.79</v>
+        <v>159790000</v>
       </c>
       <c r="AH274" t="n">
-        <v>182.99</v>
+        <v>182990000</v>
       </c>
       <c r="AI274" t="n">
         <v>590.3099999999999</v>
@@ -41829,6 +43279,12 @@
       </c>
       <c r="BB274" t="n">
         <v>238.88</v>
+      </c>
+      <c r="BC274" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD274" t="n">
+        <v>-550854</v>
       </c>
     </row>
     <row r="275">
@@ -41922,10 +43378,10 @@
         <v>7.73</v>
       </c>
       <c r="AG275" t="n">
-        <v>913</v>
+        <v>913000000</v>
       </c>
       <c r="AH275" t="n">
-        <v>926</v>
+        <v>926000000</v>
       </c>
       <c r="AI275" t="n">
         <v>410</v>
@@ -41986,6 +43442,12 @@
       </c>
       <c r="BB275" t="n">
         <v>260.67</v>
+      </c>
+      <c r="BC275" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD275" t="n">
+        <v>154</v>
       </c>
     </row>
     <row r="276">
@@ -42076,10 +43538,10 @@
         <v>130.39</v>
       </c>
       <c r="AG276" t="n">
-        <v>2120</v>
+        <v>2120000000</v>
       </c>
       <c r="AH276" t="n">
-        <v>1970</v>
+        <v>1970000000</v>
       </c>
       <c r="AI276" t="n">
         <v>1950</v>
@@ -42134,6 +43596,12 @@
       </c>
       <c r="BB276" t="n">
         <v>70.97</v>
+      </c>
+      <c r="BC276" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD276" t="n">
+        <v>180568</v>
       </c>
     </row>
     <row r="277">
@@ -42227,10 +43695,10 @@
         <v>-63.98</v>
       </c>
       <c r="AG277" t="n">
-        <v>911</v>
+        <v>911000000</v>
       </c>
       <c r="AH277" t="n">
-        <v>950</v>
+        <v>950000000</v>
       </c>
       <c r="AI277" t="n">
         <v>1020</v>
@@ -42288,6 +43756,12 @@
       </c>
       <c r="BB277" t="n">
         <v>375.26</v>
+      </c>
+      <c r="BC277" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD277" t="n">
+        <v>-650</v>
       </c>
     </row>
     <row r="278">
@@ -42381,10 +43855,10 @@
         <v>26.64</v>
       </c>
       <c r="AG278" t="n">
-        <v>91.81</v>
+        <v>91810000</v>
       </c>
       <c r="AH278" t="n">
-        <v>94.14</v>
+        <v>94140000</v>
       </c>
       <c r="AI278" t="n">
         <v>31.15</v>
@@ -42445,6 +43919,12 @@
       </c>
       <c r="BB278" t="n">
         <v>77.08</v>
+      </c>
+      <c r="BC278" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD278" t="n">
+        <v>-81784</v>
       </c>
     </row>
     <row r="279">
@@ -42538,10 +44018,10 @@
         <v>-3.99</v>
       </c>
       <c r="AG279" t="n">
-        <v>64.59999999999999</v>
+        <v>64600000</v>
       </c>
       <c r="AH279" t="n">
-        <v>70.97</v>
+        <v>70970000</v>
       </c>
       <c r="AI279" t="n">
         <v>143</v>
@@ -42602,6 +44082,12 @@
       </c>
       <c r="BB279" t="n">
         <v>1006.25</v>
+      </c>
+      <c r="BC279" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD279" t="n">
+        <v>-1466</v>
       </c>
     </row>
     <row r="280">
@@ -42695,10 +44181,10 @@
         <v>10.88</v>
       </c>
       <c r="AG280" t="n">
-        <v>1970</v>
+        <v>1970000000</v>
       </c>
       <c r="AH280" t="n">
-        <v>2140</v>
+        <v>2140000000</v>
       </c>
       <c r="AI280" t="n">
         <v>919</v>
@@ -42756,6 +44242,12 @@
       </c>
       <c r="BB280" t="n">
         <v>370.93</v>
+      </c>
+      <c r="BC280" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD280" t="n">
+        <v>-122284</v>
       </c>
     </row>
     <row r="281">
@@ -42849,10 +44341,10 @@
         <v>-15.48</v>
       </c>
       <c r="AG281" t="n">
-        <v>30</v>
+        <v>30000000</v>
       </c>
       <c r="AH281" t="n">
-        <v>30.01</v>
+        <v>30010000</v>
       </c>
       <c r="AI281" t="n">
         <v>5.2</v>
@@ -43000,10 +44492,10 @@
         <v>12.7</v>
       </c>
       <c r="AG282" t="n">
-        <v>4270</v>
+        <v>4270000000</v>
       </c>
       <c r="AH282" t="n">
-        <v>4640</v>
+        <v>4640000000</v>
       </c>
       <c r="AI282" t="n">
         <v>9.48</v>
@@ -43052,6 +44544,9 @@
       </c>
       <c r="BB282" t="n">
         <v>14.13</v>
+      </c>
+      <c r="BD282" t="n">
+        <v>426</v>
       </c>
     </row>
     <row r="283">
@@ -43142,10 +44637,10 @@
         <v>30.49</v>
       </c>
       <c r="AG283" t="n">
-        <v>167</v>
+        <v>167000000</v>
       </c>
       <c r="AH283" t="n">
-        <v>162.44</v>
+        <v>162440000</v>
       </c>
       <c r="AI283" t="n">
         <v>494.59</v>
@@ -43203,6 +44698,12 @@
       </c>
       <c r="BB283" t="n">
         <v>264.9</v>
+      </c>
+      <c r="BC283" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD283" t="n">
+        <v>-29135</v>
       </c>
     </row>
     <row r="284">
@@ -43290,10 +44791,10 @@
         <v>58.84</v>
       </c>
       <c r="AG284" t="n">
-        <v>45.45</v>
+        <v>45450000</v>
       </c>
       <c r="AH284" t="n">
-        <v>44.89</v>
+        <v>44890000</v>
       </c>
       <c r="AI284" t="n">
         <v>16.76</v>
@@ -43354,6 +44855,12 @@
       </c>
       <c r="BB284" t="n">
         <v>183.91</v>
+      </c>
+      <c r="BC284" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD284" t="n">
+        <v>-231429</v>
       </c>
     </row>
     <row r="285">
@@ -43444,10 +44951,10 @@
         <v>57.41</v>
       </c>
       <c r="AG285" t="n">
-        <v>446.42</v>
+        <v>446420000</v>
       </c>
       <c r="AH285" t="n">
-        <v>406.2</v>
+        <v>406200000</v>
       </c>
       <c r="AI285" t="n">
         <v>90.04000000000001</v>
@@ -43499,6 +45006,12 @@
       </c>
       <c r="BB285" t="n">
         <v>85.38</v>
+      </c>
+      <c r="BC285" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD285" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -43592,10 +45105,10 @@
         <v>8.279999999999999</v>
       </c>
       <c r="AG286" t="n">
-        <v>140.08</v>
+        <v>140080000</v>
       </c>
       <c r="AH286" t="n">
-        <v>158.93</v>
+        <v>158930000</v>
       </c>
       <c r="AI286" t="n">
         <v>57.6</v>
@@ -43646,10 +45159,16 @@
         <v>10.91</v>
       </c>
       <c r="BA286" t="n">
-        <v>-28.55</v>
+        <v>-28.07</v>
       </c>
       <c r="BB286" t="n">
         <v>181.75</v>
+      </c>
+      <c r="BC286" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD286" t="n">
+        <v>-11699</v>
       </c>
     </row>
     <row r="287">
@@ -43743,10 +45262,10 @@
         <v>32.13</v>
       </c>
       <c r="AG287" t="n">
-        <v>390.65</v>
+        <v>390650000</v>
       </c>
       <c r="AH287" t="n">
-        <v>378.22</v>
+        <v>378220000</v>
       </c>
       <c r="AI287" t="n">
         <v>52.2</v>
@@ -43807,6 +45326,12 @@
       </c>
       <c r="BB287" t="n">
         <v>239.41</v>
+      </c>
+      <c r="BC287" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD287" t="n">
+        <v>-133782</v>
       </c>
     </row>
     <row r="288">
@@ -43897,10 +45422,10 @@
         <v>13.58</v>
       </c>
       <c r="AG288" t="n">
-        <v>258</v>
+        <v>258000000</v>
       </c>
       <c r="AH288" t="n">
-        <v>259.1</v>
+        <v>259100000</v>
       </c>
       <c r="AI288" t="n">
         <v>689.1</v>
@@ -43961,6 +45486,12 @@
       </c>
       <c r="BB288" t="n">
         <v>513.26</v>
+      </c>
+      <c r="BC288" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BD288" t="n">
+        <v>18699</v>
       </c>
     </row>
     <row r="289">
@@ -44054,10 +45585,10 @@
         <v>103.33</v>
       </c>
       <c r="AG289" t="n">
-        <v>268.12</v>
+        <v>268120000</v>
       </c>
       <c r="AH289" t="n">
-        <v>254.82</v>
+        <v>254820000</v>
       </c>
       <c r="AI289" t="n">
         <v>1650</v>
@@ -44115,6 +45646,12 @@
       </c>
       <c r="BB289" t="n">
         <v>187.76</v>
+      </c>
+      <c r="BC289" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BD289" t="n">
+        <v>-996117</v>
       </c>
     </row>
     <row r="290">
@@ -44202,10 +45739,10 @@
         <v>137.5</v>
       </c>
       <c r="AG290" t="n">
-        <v>383</v>
+        <v>383000000</v>
       </c>
       <c r="AH290" t="n">
-        <v>318</v>
+        <v>318000000</v>
       </c>
       <c r="AI290" t="n">
         <v>195</v>
@@ -44266,6 +45803,12 @@
       </c>
       <c r="BB290" t="n">
         <v>416.97</v>
+      </c>
+      <c r="BC290" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD290" t="n">
+        <v>-24448</v>
       </c>
     </row>
     <row r="291">
@@ -44353,10 +45896,10 @@
         <v>-6.78</v>
       </c>
       <c r="AG291" t="n">
-        <v>15.07</v>
+        <v>15070000</v>
       </c>
       <c r="AH291" t="n">
-        <v>13.01</v>
+        <v>13010000</v>
       </c>
       <c r="AI291" t="n">
         <v>14.72</v>
@@ -44408,6 +45951,12 @@
       </c>
       <c r="BB291" t="n">
         <v>78.38</v>
+      </c>
+      <c r="BC291" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BD291" t="n">
+        <v>-54750</v>
       </c>
     </row>
     <row r="292">
@@ -44501,10 +46050,10 @@
         <v>10.8</v>
       </c>
       <c r="AG292" t="n">
-        <v>8020</v>
+        <v>8020000000</v>
       </c>
       <c r="AH292" t="n">
-        <v>8200</v>
+        <v>8200000000</v>
       </c>
       <c r="AI292" t="n">
         <v>3600</v>
@@ -44565,6 +46114,12 @@
       </c>
       <c r="BB292" t="n">
         <v>107.5</v>
+      </c>
+      <c r="BC292" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BD292" t="n">
+        <v>-2593058</v>
       </c>
     </row>
     <row r="293">
@@ -44577,7 +46132,7 @@
         <v>0.09</v>
       </c>
       <c r="C293" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="D293" t="n">
         <v>0.1</v>
@@ -44658,10 +46213,10 @@
         <v>12.06</v>
       </c>
       <c r="AG293" t="n">
-        <v>3410</v>
+        <v>3410000000</v>
       </c>
       <c r="AH293" t="n">
-        <v>3410</v>
+        <v>3410000000</v>
       </c>
       <c r="AJ293" t="n">
         <v>-35.1</v>
@@ -44759,7 +46314,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-17 web scrape, 52 fields (19 prior + 35 new capital/quality/valuation cols). Money=USD mm; shares=mm; Target/Last Price=local ccy. Range gate (-100..200) only on the 6 legacy pct cols.</t>
+          <t>2026-09-17 web scrape, 55 fields (19 prior + 35 fundamental-gates cols [2026-09-17] + 2 short-interest/insider cols [2026-09-17b]). Money=USD mm; shares=mm (legacy cols) or raw share count (Insider Net Buy 3M — NOT thousands/millions); Target/Last Price=local ccy. Short Interest % Float = % of float (already in % units, no ratio conversion). Insider Net Buy 3M = net shares bought minus sold, trailing 3 months, signed (positive=net buying, negative=net selling; source: Koyfin 'Insider Transactions, Shares (Net) - 3M'). Range gate (-100..200) only on the 6 legacy pct cols.</t>
         </is>
       </c>
     </row>
